--- a/output/version3/test/25-15/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1185</v>
+        <v>1128</v>
       </c>
       <c r="C2" t="n">
-        <v>1157</v>
+        <v>1294</v>
       </c>
       <c r="D2" t="n">
-        <v>1084</v>
+        <v>1302</v>
       </c>
       <c r="E2" t="n">
-        <v>1142</v>
+        <v>1228</v>
       </c>
       <c r="F2" t="n">
-        <v>1129</v>
+        <v>1172</v>
       </c>
       <c r="G2" t="n">
+        <v>1171</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="I2" t="n">
         <v>1052</v>
       </c>
-      <c r="H2" t="n">
-        <v>1104</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1203</v>
-      </c>
       <c r="J2" t="n">
-        <v>1056</v>
+        <v>1164</v>
       </c>
       <c r="K2" t="n">
-        <v>1245</v>
+        <v>1146</v>
       </c>
       <c r="L2" t="n">
-        <v>1135.7</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1199</v>
+        <v>1317</v>
       </c>
       <c r="C3" t="n">
-        <v>1171</v>
+        <v>1104</v>
       </c>
       <c r="D3" t="n">
-        <v>996</v>
+        <v>1202</v>
       </c>
       <c r="E3" t="n">
-        <v>1215</v>
+        <v>1073</v>
       </c>
       <c r="F3" t="n">
-        <v>1096</v>
+        <v>1158</v>
       </c>
       <c r="G3" t="n">
-        <v>1073</v>
+        <v>976</v>
       </c>
       <c r="H3" t="n">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="I3" t="n">
-        <v>1087</v>
+        <v>1203</v>
       </c>
       <c r="J3" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="K3" t="n">
-        <v>1050</v>
+        <v>1147</v>
       </c>
       <c r="L3" t="n">
-        <v>1099.4</v>
+        <v>1127.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1323</v>
+        <v>1196</v>
       </c>
       <c r="C4" t="n">
-        <v>1234</v>
+        <v>1163</v>
       </c>
       <c r="D4" t="n">
-        <v>1107</v>
+        <v>1171</v>
       </c>
       <c r="E4" t="n">
-        <v>1229</v>
+        <v>1109</v>
       </c>
       <c r="F4" t="n">
-        <v>1084</v>
+        <v>1100</v>
       </c>
       <c r="G4" t="n">
-        <v>1282</v>
+        <v>1091</v>
       </c>
       <c r="H4" t="n">
-        <v>1039</v>
+        <v>1119</v>
       </c>
       <c r="I4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1047</v>
+      </c>
+      <c r="K4" t="n">
         <v>1172</v>
       </c>
-      <c r="J4" t="n">
-        <v>1232</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1306</v>
-      </c>
       <c r="L4" t="n">
-        <v>1200.8</v>
+        <v>1132.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1010</v>
+        <v>1051</v>
       </c>
       <c r="C5" t="n">
-        <v>937</v>
+        <v>1029</v>
       </c>
       <c r="D5" t="n">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="E5" t="n">
-        <v>1027</v>
+        <v>920</v>
       </c>
       <c r="F5" t="n">
-        <v>1080</v>
+        <v>1055</v>
       </c>
       <c r="G5" t="n">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="H5" t="n">
-        <v>1022</v>
+        <v>1041</v>
       </c>
       <c r="I5" t="n">
-        <v>1098</v>
+        <v>1063</v>
       </c>
       <c r="J5" t="n">
-        <v>1067</v>
+        <v>1009</v>
       </c>
       <c r="K5" t="n">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="L5" t="n">
-        <v>1029.5</v>
+        <v>1025.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1096</v>
+        <v>1356</v>
       </c>
       <c r="C6" t="n">
-        <v>1111</v>
+        <v>1145</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>1116</v>
       </c>
       <c r="E6" t="n">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="F6" t="n">
         <v>1174</v>
       </c>
       <c r="G6" t="n">
-        <v>1143</v>
+        <v>1192</v>
       </c>
       <c r="H6" t="n">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="I6" t="n">
-        <v>1072</v>
+        <v>1336</v>
       </c>
       <c r="J6" t="n">
-        <v>1343</v>
+        <v>1012</v>
       </c>
       <c r="K6" t="n">
-        <v>1110</v>
+        <v>1334</v>
       </c>
       <c r="L6" t="n">
-        <v>1148.1</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="C7" t="n">
-        <v>1070</v>
+        <v>1016</v>
       </c>
       <c r="D7" t="n">
-        <v>1100</v>
+        <v>1016</v>
       </c>
       <c r="E7" t="n">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="F7" t="n">
-        <v>1017</v>
+        <v>910</v>
       </c>
       <c r="G7" t="n">
-        <v>1042</v>
+        <v>1021</v>
       </c>
       <c r="H7" t="n">
-        <v>1128</v>
+        <v>1166</v>
       </c>
       <c r="I7" t="n">
-        <v>1206</v>
+        <v>1028</v>
       </c>
       <c r="J7" t="n">
-        <v>1067</v>
+        <v>987</v>
       </c>
       <c r="K7" t="n">
-        <v>974</v>
+        <v>1027</v>
       </c>
       <c r="L7" t="n">
-        <v>1081.8</v>
+        <v>1037.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1223</v>
+        <v>1146</v>
       </c>
       <c r="C8" t="n">
-        <v>1016</v>
+        <v>1174</v>
       </c>
       <c r="D8" t="n">
-        <v>1073</v>
+        <v>1193</v>
       </c>
       <c r="E8" t="n">
-        <v>1216</v>
+        <v>999</v>
       </c>
       <c r="F8" t="n">
-        <v>1047</v>
+        <v>1214</v>
       </c>
       <c r="G8" t="n">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="H8" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="I8" t="n">
-        <v>1035</v>
+        <v>1296</v>
       </c>
       <c r="J8" t="n">
-        <v>1112</v>
+        <v>911</v>
       </c>
       <c r="K8" t="n">
-        <v>1205</v>
+        <v>1275</v>
       </c>
       <c r="L8" t="n">
-        <v>1121.4</v>
+        <v>1150.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1244</v>
+        <v>1117</v>
       </c>
       <c r="C9" t="n">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="D9" t="n">
-        <v>1168</v>
+        <v>1041</v>
       </c>
       <c r="E9" t="n">
-        <v>1091</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="n">
-        <v>1112</v>
+        <v>955</v>
       </c>
       <c r="G9" t="n">
-        <v>1105</v>
+        <v>1052</v>
       </c>
       <c r="H9" t="n">
-        <v>1128</v>
+        <v>972</v>
       </c>
       <c r="I9" t="n">
-        <v>1136</v>
+        <v>1152</v>
       </c>
       <c r="J9" t="n">
-        <v>1144</v>
+        <v>1099</v>
       </c>
       <c r="K9" t="n">
-        <v>1070</v>
+        <v>990</v>
       </c>
       <c r="L9" t="n">
-        <v>1122.2</v>
+        <v>1044.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>1179</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D10" t="n">
         <v>1060</v>
       </c>
-      <c r="C10" t="n">
-        <v>1201</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1239</v>
-      </c>
       <c r="E10" t="n">
-        <v>1176</v>
+        <v>1248</v>
       </c>
       <c r="F10" t="n">
-        <v>1127</v>
+        <v>1027</v>
       </c>
       <c r="G10" t="n">
-        <v>1040</v>
+        <v>1143</v>
       </c>
       <c r="H10" t="n">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="I10" t="n">
-        <v>1124</v>
+        <v>971</v>
       </c>
       <c r="J10" t="n">
-        <v>1077</v>
+        <v>1117</v>
       </c>
       <c r="K10" t="n">
-        <v>1024</v>
+        <v>1043</v>
       </c>
       <c r="L10" t="n">
-        <v>1129.8</v>
+        <v>1106.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1362</v>
+        <v>1133</v>
       </c>
       <c r="C11" t="n">
-        <v>1133</v>
+        <v>1162</v>
       </c>
       <c r="D11" t="n">
-        <v>1112</v>
+        <v>1137</v>
       </c>
       <c r="E11" t="n">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="F11" t="n">
-        <v>1024</v>
+        <v>1170</v>
       </c>
       <c r="G11" t="n">
-        <v>1168</v>
+        <v>1222</v>
       </c>
       <c r="H11" t="n">
-        <v>994</v>
+        <v>1076</v>
       </c>
       <c r="I11" t="n">
-        <v>1258</v>
+        <v>1182</v>
       </c>
       <c r="J11" t="n">
-        <v>1271</v>
+        <v>1122</v>
       </c>
       <c r="K11" t="n">
-        <v>1172</v>
+        <v>1108</v>
       </c>
       <c r="L11" t="n">
-        <v>1178</v>
+        <v>1159.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1181</v>
+        <v>1482</v>
       </c>
       <c r="C12" t="n">
-        <v>1026</v>
+        <v>1131</v>
       </c>
       <c r="D12" t="n">
-        <v>1170</v>
+        <v>1333</v>
       </c>
       <c r="E12" t="n">
-        <v>1382</v>
+        <v>1225</v>
       </c>
       <c r="F12" t="n">
-        <v>1331</v>
+        <v>1073</v>
       </c>
       <c r="G12" t="n">
-        <v>1170</v>
+        <v>1408</v>
       </c>
       <c r="H12" t="n">
-        <v>1067</v>
+        <v>1110</v>
       </c>
       <c r="I12" t="n">
-        <v>1330</v>
+        <v>1216</v>
       </c>
       <c r="J12" t="n">
-        <v>1218</v>
+        <v>1408</v>
       </c>
       <c r="K12" t="n">
-        <v>1243</v>
+        <v>1288</v>
       </c>
       <c r="L12" t="n">
-        <v>1211.8</v>
+        <v>1267.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1275</v>
+        <v>1214</v>
       </c>
       <c r="C13" t="n">
-        <v>1267</v>
+        <v>1289</v>
       </c>
       <c r="D13" t="n">
-        <v>1368</v>
+        <v>1348</v>
       </c>
       <c r="E13" t="n">
-        <v>1179</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="n">
-        <v>1280</v>
+        <v>1369</v>
       </c>
       <c r="G13" t="n">
-        <v>1247</v>
+        <v>1140</v>
       </c>
       <c r="H13" t="n">
-        <v>1434</v>
+        <v>1226</v>
       </c>
       <c r="I13" t="n">
-        <v>1457</v>
+        <v>1283</v>
       </c>
       <c r="J13" t="n">
-        <v>1279</v>
+        <v>1151</v>
       </c>
       <c r="K13" t="n">
-        <v>1150</v>
+        <v>1385</v>
       </c>
       <c r="L13" t="n">
-        <v>1293.6</v>
+        <v>1276.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1139</v>
+        <v>984</v>
       </c>
       <c r="C14" t="n">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="D14" t="n">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="E14" t="n">
-        <v>1176</v>
+        <v>1145</v>
       </c>
       <c r="F14" t="n">
-        <v>968</v>
+        <v>871</v>
       </c>
       <c r="G14" t="n">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="H14" t="n">
-        <v>986</v>
+        <v>1285</v>
       </c>
       <c r="I14" t="n">
-        <v>942</v>
+        <v>1103</v>
       </c>
       <c r="J14" t="n">
-        <v>1199</v>
+        <v>1114</v>
       </c>
       <c r="K14" t="n">
-        <v>1026</v>
+        <v>1079</v>
       </c>
       <c r="L14" t="n">
-        <v>1063.4</v>
+        <v>1076.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1146</v>
+        <v>1042</v>
       </c>
       <c r="C15" t="n">
-        <v>1024</v>
+        <v>1043</v>
       </c>
       <c r="D15" t="n">
-        <v>1374</v>
+        <v>959</v>
       </c>
       <c r="E15" t="n">
-        <v>1054</v>
+        <v>1019</v>
       </c>
       <c r="F15" t="n">
-        <v>1174</v>
+        <v>1046</v>
       </c>
       <c r="G15" t="n">
-        <v>1127</v>
+        <v>1150</v>
       </c>
       <c r="H15" t="n">
-        <v>1083</v>
+        <v>1115</v>
       </c>
       <c r="I15" t="n">
-        <v>1083</v>
+        <v>1131</v>
       </c>
       <c r="J15" t="n">
-        <v>1195</v>
+        <v>1053</v>
       </c>
       <c r="K15" t="n">
-        <v>976</v>
+        <v>1107</v>
       </c>
       <c r="L15" t="n">
-        <v>1123.6</v>
+        <v>1066.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1306</v>
+        <v>1122</v>
       </c>
       <c r="C16" t="n">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="D16" t="n">
-        <v>1021</v>
+        <v>1100</v>
       </c>
       <c r="E16" t="n">
-        <v>1423</v>
+        <v>982</v>
       </c>
       <c r="F16" t="n">
-        <v>1224</v>
+        <v>1250</v>
       </c>
       <c r="G16" t="n">
-        <v>1034</v>
+        <v>1075</v>
       </c>
       <c r="H16" t="n">
-        <v>1208</v>
+        <v>1297</v>
       </c>
       <c r="I16" t="n">
-        <v>1223</v>
+        <v>1392</v>
       </c>
       <c r="J16" t="n">
-        <v>1268</v>
+        <v>997</v>
       </c>
       <c r="K16" t="n">
-        <v>1033</v>
+        <v>1138</v>
       </c>
       <c r="L16" t="n">
-        <v>1200.5</v>
+        <v>1164.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1077</v>
+        <v>1043</v>
       </c>
       <c r="C17" t="n">
-        <v>1157</v>
+        <v>1095</v>
       </c>
       <c r="D17" t="n">
-        <v>1117</v>
+        <v>1044</v>
       </c>
       <c r="E17" t="n">
-        <v>1002</v>
+        <v>1375</v>
       </c>
       <c r="F17" t="n">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="G17" t="n">
-        <v>1162</v>
+        <v>967</v>
       </c>
       <c r="H17" t="n">
-        <v>1031</v>
+        <v>1075</v>
       </c>
       <c r="I17" t="n">
-        <v>1120</v>
+        <v>1049</v>
       </c>
       <c r="J17" t="n">
-        <v>959</v>
+        <v>1049</v>
       </c>
       <c r="K17" t="n">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="L17" t="n">
-        <v>1076.5</v>
+        <v>1083.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1187</v>
+        <v>1225</v>
       </c>
       <c r="C18" t="n">
-        <v>1248</v>
+        <v>1317</v>
       </c>
       <c r="D18" t="n">
-        <v>993</v>
+        <v>1086</v>
       </c>
       <c r="E18" t="n">
-        <v>1196</v>
+        <v>1088</v>
       </c>
       <c r="F18" t="n">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="G18" t="n">
-        <v>1245</v>
+        <v>1010</v>
       </c>
       <c r="H18" t="n">
-        <v>1225</v>
+        <v>1101</v>
       </c>
       <c r="I18" t="n">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="J18" t="n">
-        <v>1238</v>
+        <v>1106</v>
       </c>
       <c r="K18" t="n">
-        <v>1218</v>
+        <v>1079</v>
       </c>
       <c r="L18" t="n">
-        <v>1181.8</v>
+        <v>1126.3</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1195</v>
+        <v>1233</v>
       </c>
       <c r="C19" t="n">
-        <v>1189</v>
+        <v>1251</v>
       </c>
       <c r="D19" t="n">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="E19" t="n">
-        <v>1018</v>
+        <v>1124</v>
       </c>
       <c r="F19" t="n">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="G19" t="n">
-        <v>1136</v>
+        <v>1081</v>
       </c>
       <c r="H19" t="n">
-        <v>1252</v>
+        <v>1289</v>
       </c>
       <c r="I19" t="n">
-        <v>1312</v>
+        <v>1323</v>
       </c>
       <c r="J19" t="n">
-        <v>1378</v>
+        <v>1225</v>
       </c>
       <c r="K19" t="n">
-        <v>1390</v>
+        <v>1188</v>
       </c>
       <c r="L19" t="n">
-        <v>1226.9</v>
+        <v>1219.3</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1410</v>
+        <v>1345</v>
       </c>
       <c r="C20" t="n">
-        <v>1279</v>
+        <v>1215</v>
       </c>
       <c r="D20" t="n">
-        <v>1109</v>
+        <v>1189</v>
       </c>
       <c r="E20" t="n">
-        <v>1110</v>
+        <v>1062</v>
       </c>
       <c r="F20" t="n">
-        <v>1075</v>
+        <v>1241</v>
       </c>
       <c r="G20" t="n">
-        <v>1077</v>
+        <v>1297</v>
       </c>
       <c r="H20" t="n">
-        <v>1211</v>
+        <v>1128</v>
       </c>
       <c r="I20" t="n">
-        <v>1077</v>
+        <v>1373</v>
       </c>
       <c r="J20" t="n">
-        <v>1188</v>
+        <v>1288</v>
       </c>
       <c r="K20" t="n">
-        <v>1044</v>
+        <v>1241</v>
       </c>
       <c r="L20" t="n">
-        <v>1158</v>
+        <v>1237.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="C21" t="n">
-        <v>1125</v>
+        <v>1176</v>
       </c>
       <c r="D21" t="n">
-        <v>1081</v>
+        <v>1153</v>
       </c>
       <c r="E21" t="n">
-        <v>1283</v>
+        <v>1100</v>
       </c>
       <c r="F21" t="n">
-        <v>1140</v>
+        <v>1171</v>
       </c>
       <c r="G21" t="n">
-        <v>1204</v>
+        <v>1226</v>
       </c>
       <c r="H21" t="n">
-        <v>1191</v>
+        <v>1073</v>
       </c>
       <c r="I21" t="n">
-        <v>1173</v>
+        <v>1090</v>
       </c>
       <c r="J21" t="n">
-        <v>1157</v>
+        <v>1232</v>
       </c>
       <c r="K21" t="n">
-        <v>1157</v>
+        <v>1136</v>
       </c>
       <c r="L21" t="n">
-        <v>1162.4</v>
+        <v>1147.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1405</v>
+        <v>1347</v>
       </c>
       <c r="C22" t="n">
-        <v>1196</v>
+        <v>1129</v>
       </c>
       <c r="D22" t="n">
-        <v>1211</v>
+        <v>1264</v>
       </c>
       <c r="E22" t="n">
-        <v>1275</v>
+        <v>1193</v>
       </c>
       <c r="F22" t="n">
-        <v>1078</v>
+        <v>1301</v>
       </c>
       <c r="G22" t="n">
-        <v>1108</v>
+        <v>1291</v>
       </c>
       <c r="H22" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="I22" t="n">
-        <v>1245</v>
+        <v>1200</v>
       </c>
       <c r="J22" t="n">
-        <v>1143</v>
+        <v>1209</v>
       </c>
       <c r="K22" t="n">
-        <v>1136</v>
+        <v>1261</v>
       </c>
       <c r="L22" t="n">
-        <v>1194.1</v>
+        <v>1237.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1278</v>
+        <v>1259</v>
       </c>
       <c r="C23" t="n">
-        <v>1074</v>
+        <v>1135</v>
       </c>
       <c r="D23" t="n">
-        <v>1008</v>
+        <v>1145</v>
       </c>
       <c r="E23" t="n">
-        <v>1184</v>
+        <v>1152</v>
       </c>
       <c r="F23" t="n">
-        <v>1221</v>
+        <v>980</v>
       </c>
       <c r="G23" t="n">
-        <v>1038</v>
+        <v>1265</v>
       </c>
       <c r="H23" t="n">
-        <v>1141</v>
+        <v>1312</v>
       </c>
       <c r="I23" t="n">
-        <v>1292</v>
+        <v>1066</v>
       </c>
       <c r="J23" t="n">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="K23" t="n">
-        <v>1001</v>
+        <v>1233</v>
       </c>
       <c r="L23" t="n">
-        <v>1126.1</v>
+        <v>1155.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1070</v>
+        <v>1142</v>
       </c>
       <c r="C24" t="n">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D24" t="n">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="E24" t="n">
-        <v>1230</v>
+        <v>1175</v>
       </c>
       <c r="F24" t="n">
-        <v>1304</v>
+        <v>1155</v>
       </c>
       <c r="G24" t="n">
-        <v>1291</v>
+        <v>1166</v>
       </c>
       <c r="H24" t="n">
-        <v>1108</v>
+        <v>1297</v>
       </c>
       <c r="I24" t="n">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="J24" t="n">
-        <v>1082</v>
+        <v>1204</v>
       </c>
       <c r="K24" t="n">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="L24" t="n">
-        <v>1153.4</v>
+        <v>1159.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1057</v>
+        <v>1235</v>
       </c>
       <c r="C25" t="n">
-        <v>1196</v>
+        <v>1143</v>
       </c>
       <c r="D25" t="n">
-        <v>1289</v>
+        <v>1055</v>
       </c>
       <c r="E25" t="n">
-        <v>1061</v>
+        <v>995</v>
       </c>
       <c r="F25" t="n">
-        <v>1217</v>
+        <v>1274</v>
       </c>
       <c r="G25" t="n">
-        <v>1144</v>
+        <v>1053</v>
       </c>
       <c r="H25" t="n">
-        <v>1357</v>
+        <v>1326</v>
       </c>
       <c r="I25" t="n">
-        <v>1169</v>
+        <v>1139</v>
       </c>
       <c r="J25" t="n">
-        <v>1333</v>
+        <v>1190</v>
       </c>
       <c r="K25" t="n">
-        <v>1225</v>
+        <v>1197</v>
       </c>
       <c r="L25" t="n">
-        <v>1204.8</v>
+        <v>1160.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
+        <v>1021</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1093</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1098</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1098</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1054</v>
+      </c>
+      <c r="K26" t="n">
         <v>1070</v>
       </c>
-      <c r="C26" t="n">
-        <v>1098</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1176</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1103</v>
-      </c>
-      <c r="F26" t="n">
-        <v>994</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1031</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1279</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1339</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1274</v>
-      </c>
-      <c r="K26" t="n">
-        <v>976</v>
-      </c>
       <c r="L26" t="n">
-        <v>1134</v>
+        <v>1062.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1463</v>
+        <v>1086</v>
       </c>
       <c r="C27" t="n">
-        <v>1268</v>
+        <v>1198</v>
       </c>
       <c r="D27" t="n">
-        <v>1114</v>
+        <v>1094</v>
       </c>
       <c r="E27" t="n">
-        <v>1111</v>
+        <v>1327</v>
       </c>
       <c r="F27" t="n">
-        <v>1135</v>
+        <v>1401</v>
       </c>
       <c r="G27" t="n">
+        <v>1079</v>
+      </c>
+      <c r="H27" t="n">
         <v>1175</v>
       </c>
-      <c r="H27" t="n">
-        <v>1115</v>
-      </c>
       <c r="I27" t="n">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="J27" t="n">
-        <v>1145</v>
+        <v>1206</v>
       </c>
       <c r="K27" t="n">
-        <v>1292</v>
+        <v>1157</v>
       </c>
       <c r="L27" t="n">
-        <v>1199.3</v>
+        <v>1188.8</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1046</v>
+        <v>1123</v>
       </c>
       <c r="C28" t="n">
-        <v>1134</v>
+        <v>1328</v>
       </c>
       <c r="D28" t="n">
-        <v>1214</v>
+        <v>1158</v>
       </c>
       <c r="E28" t="n">
-        <v>1292</v>
+        <v>1043</v>
       </c>
       <c r="F28" t="n">
-        <v>1010</v>
+        <v>1146</v>
       </c>
       <c r="G28" t="n">
-        <v>1194</v>
+        <v>1025</v>
       </c>
       <c r="H28" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="I28" t="n">
-        <v>1251</v>
+        <v>1093</v>
       </c>
       <c r="J28" t="n">
-        <v>1200</v>
+        <v>1055</v>
       </c>
       <c r="K28" t="n">
-        <v>1022</v>
+        <v>1105</v>
       </c>
       <c r="L28" t="n">
-        <v>1139.6</v>
+        <v>1110.6</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="C29" t="n">
-        <v>1087</v>
+        <v>1156</v>
       </c>
       <c r="D29" t="n">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="E29" t="n">
-        <v>1210</v>
+        <v>1078</v>
       </c>
       <c r="F29" t="n">
-        <v>1008</v>
+        <v>1052</v>
       </c>
       <c r="G29" t="n">
-        <v>1041</v>
+        <v>951</v>
       </c>
       <c r="H29" t="n">
-        <v>1252</v>
+        <v>1064</v>
       </c>
       <c r="I29" t="n">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="J29" t="n">
-        <v>1116</v>
+        <v>1092</v>
       </c>
       <c r="K29" t="n">
-        <v>1187</v>
+        <v>1170</v>
       </c>
       <c r="L29" t="n">
-        <v>1097.8</v>
+        <v>1066.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1170</v>
+        <v>1051</v>
       </c>
       <c r="C30" t="n">
-        <v>1289</v>
+        <v>1040</v>
       </c>
       <c r="D30" t="n">
-        <v>1205</v>
+        <v>1188</v>
       </c>
       <c r="E30" t="n">
-        <v>1210</v>
+        <v>1027</v>
       </c>
       <c r="F30" t="n">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G30" t="n">
-        <v>1136</v>
+        <v>1088</v>
       </c>
       <c r="H30" t="n">
-        <v>985</v>
+        <v>1034</v>
       </c>
       <c r="I30" t="n">
-        <v>1165</v>
+        <v>978</v>
       </c>
       <c r="J30" t="n">
-        <v>1139</v>
+        <v>1228</v>
       </c>
       <c r="K30" t="n">
-        <v>1135</v>
+        <v>1184</v>
       </c>
       <c r="L30" t="n">
-        <v>1149.8</v>
+        <v>1088.3</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="C31" t="n">
-        <v>1175</v>
+        <v>1204</v>
       </c>
       <c r="D31" t="n">
-        <v>1109</v>
+        <v>1189</v>
       </c>
       <c r="E31" t="n">
-        <v>1160</v>
+        <v>1045</v>
       </c>
       <c r="F31" t="n">
-        <v>1081</v>
+        <v>1220</v>
       </c>
       <c r="G31" t="n">
-        <v>1088</v>
+        <v>1233</v>
       </c>
       <c r="H31" t="n">
-        <v>1323</v>
+        <v>1116</v>
       </c>
       <c r="I31" t="n">
-        <v>1194</v>
+        <v>1090</v>
       </c>
       <c r="J31" t="n">
-        <v>1110</v>
+        <v>1130</v>
       </c>
       <c r="K31" t="n">
-        <v>1155</v>
+        <v>1213</v>
       </c>
       <c r="L31" t="n">
-        <v>1158.9</v>
+        <v>1163.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="C32" t="n">
-        <v>1179</v>
+        <v>984</v>
       </c>
       <c r="D32" t="n">
-        <v>1138</v>
+        <v>1021</v>
       </c>
       <c r="E32" t="n">
-        <v>1043</v>
+        <v>907</v>
       </c>
       <c r="F32" t="n">
-        <v>965</v>
+        <v>1120</v>
       </c>
       <c r="G32" t="n">
-        <v>962</v>
+        <v>926</v>
       </c>
       <c r="H32" t="n">
-        <v>1019</v>
+        <v>905</v>
       </c>
       <c r="I32" t="n">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="J32" t="n">
-        <v>1021</v>
+        <v>944</v>
       </c>
       <c r="K32" t="n">
-        <v>948</v>
+        <v>1301</v>
       </c>
       <c r="L32" t="n">
-        <v>1032.5</v>
+        <v>1013.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1115</v>
+        <v>1287</v>
       </c>
       <c r="C33" t="n">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="D33" t="n">
-        <v>1064</v>
+        <v>1152</v>
       </c>
       <c r="E33" t="n">
-        <v>1154</v>
+        <v>1137</v>
       </c>
       <c r="F33" t="n">
-        <v>1041</v>
+        <v>1059</v>
       </c>
       <c r="G33" t="n">
-        <v>1149</v>
+        <v>1110</v>
       </c>
       <c r="H33" t="n">
-        <v>1206</v>
+        <v>1081</v>
       </c>
       <c r="I33" t="n">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="J33" t="n">
-        <v>1058</v>
+        <v>1095</v>
       </c>
       <c r="K33" t="n">
-        <v>1104</v>
+        <v>1311</v>
       </c>
       <c r="L33" t="n">
-        <v>1113</v>
+        <v>1146.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1144</v>
+        <v>1225</v>
       </c>
       <c r="C34" t="n">
-        <v>1138</v>
+        <v>969</v>
       </c>
       <c r="D34" t="n">
-        <v>1228</v>
+        <v>1161</v>
       </c>
       <c r="E34" t="n">
-        <v>1061</v>
+        <v>1317</v>
       </c>
       <c r="F34" t="n">
-        <v>1047</v>
+        <v>1162</v>
       </c>
       <c r="G34" t="n">
-        <v>1339</v>
+        <v>1016</v>
       </c>
       <c r="H34" t="n">
-        <v>1278</v>
+        <v>1106</v>
       </c>
       <c r="I34" t="n">
-        <v>1089</v>
+        <v>1245</v>
       </c>
       <c r="J34" t="n">
-        <v>1149</v>
+        <v>1076</v>
       </c>
       <c r="K34" t="n">
-        <v>1272</v>
+        <v>1345</v>
       </c>
       <c r="L34" t="n">
-        <v>1174.5</v>
+        <v>1162.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="C35" t="n">
-        <v>1154</v>
+        <v>1112</v>
       </c>
       <c r="D35" t="n">
-        <v>1166</v>
+        <v>1003</v>
       </c>
       <c r="E35" t="n">
-        <v>1127</v>
+        <v>1234</v>
       </c>
       <c r="F35" t="n">
-        <v>1142</v>
+        <v>1344</v>
       </c>
       <c r="G35" t="n">
-        <v>1053</v>
+        <v>1293</v>
       </c>
       <c r="H35" t="n">
-        <v>1052</v>
+        <v>1164</v>
       </c>
       <c r="I35" t="n">
-        <v>1163</v>
+        <v>1086</v>
       </c>
       <c r="J35" t="n">
-        <v>1192</v>
+        <v>1088</v>
       </c>
       <c r="K35" t="n">
-        <v>1145</v>
+        <v>1110</v>
       </c>
       <c r="L35" t="n">
-        <v>1126.5</v>
+        <v>1149.6</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1114</v>
+        <v>1308</v>
       </c>
       <c r="C36" t="n">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="D36" t="n">
-        <v>1102</v>
+        <v>1182</v>
       </c>
       <c r="E36" t="n">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="F36" t="n">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="G36" t="n">
-        <v>981</v>
+        <v>1018</v>
       </c>
       <c r="H36" t="n">
-        <v>1249</v>
+        <v>1170</v>
       </c>
       <c r="I36" t="n">
-        <v>1159</v>
+        <v>1072</v>
       </c>
       <c r="J36" t="n">
-        <v>1211</v>
+        <v>1111</v>
       </c>
       <c r="K36" t="n">
-        <v>1170</v>
+        <v>1061</v>
       </c>
       <c r="L36" t="n">
-        <v>1131</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1240</v>
+        <v>1101</v>
       </c>
       <c r="C37" t="n">
-        <v>1185</v>
+        <v>1226</v>
       </c>
       <c r="D37" t="n">
-        <v>1238</v>
+        <v>1146</v>
       </c>
       <c r="E37" t="n">
-        <v>1199</v>
+        <v>1093</v>
       </c>
       <c r="F37" t="n">
-        <v>1049</v>
+        <v>1242</v>
       </c>
       <c r="G37" t="n">
-        <v>1146</v>
+        <v>1107</v>
       </c>
       <c r="H37" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="I37" t="n">
-        <v>1124</v>
+        <v>1293</v>
       </c>
       <c r="J37" t="n">
-        <v>1195</v>
+        <v>1249</v>
       </c>
       <c r="K37" t="n">
-        <v>1218</v>
+        <v>1249</v>
       </c>
       <c r="L37" t="n">
-        <v>1182.5</v>
+        <v>1192.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>940</v>
+        <v>1225</v>
       </c>
       <c r="C38" t="n">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="D38" t="n">
-        <v>984</v>
+        <v>1147</v>
       </c>
       <c r="E38" t="n">
-        <v>1042</v>
+        <v>1100</v>
       </c>
       <c r="F38" t="n">
-        <v>1033</v>
+        <v>1154</v>
       </c>
       <c r="G38" t="n">
-        <v>1071</v>
+        <v>1114</v>
       </c>
       <c r="H38" t="n">
-        <v>1039</v>
+        <v>1282</v>
       </c>
       <c r="I38" t="n">
-        <v>1081</v>
+        <v>991</v>
       </c>
       <c r="J38" t="n">
-        <v>903</v>
+        <v>986</v>
       </c>
       <c r="K38" t="n">
-        <v>1114</v>
+        <v>1053</v>
       </c>
       <c r="L38" t="n">
-        <v>1027.4</v>
+        <v>1110.4</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1312</v>
+        <v>1061</v>
       </c>
       <c r="C39" t="n">
-        <v>1184</v>
+        <v>1382</v>
       </c>
       <c r="D39" t="n">
-        <v>1007</v>
+        <v>1054</v>
       </c>
       <c r="E39" t="n">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="F39" t="n">
-        <v>1030</v>
+        <v>1115</v>
       </c>
       <c r="G39" t="n">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="H39" t="n">
-        <v>1311</v>
+        <v>1137</v>
       </c>
       <c r="I39" t="n">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="J39" t="n">
-        <v>1094</v>
+        <v>1147</v>
       </c>
       <c r="K39" t="n">
-        <v>1062</v>
+        <v>1226</v>
       </c>
       <c r="L39" t="n">
-        <v>1128.5</v>
+        <v>1137.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
+        <v>1248</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1089</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1268</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1107</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1035</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1248</v>
+      </c>
+      <c r="J40" t="n">
         <v>1168</v>
       </c>
-      <c r="C40" t="n">
-        <v>1095</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1342</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1171</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1175</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1284</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1338</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1169</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1212</v>
-      </c>
       <c r="K40" t="n">
-        <v>1304</v>
+        <v>970</v>
       </c>
       <c r="L40" t="n">
-        <v>1225.8</v>
+        <v>1130.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>981</v>
+        <v>1242</v>
       </c>
       <c r="C41" t="n">
-        <v>997</v>
+        <v>1192</v>
       </c>
       <c r="D41" t="n">
-        <v>1045</v>
+        <v>900</v>
       </c>
       <c r="E41" t="n">
-        <v>1161</v>
+        <v>1131</v>
       </c>
       <c r="F41" t="n">
-        <v>1115</v>
+        <v>996</v>
       </c>
       <c r="G41" t="n">
-        <v>1153</v>
+        <v>1213</v>
       </c>
       <c r="H41" t="n">
-        <v>1059</v>
+        <v>1205</v>
       </c>
       <c r="I41" t="n">
-        <v>1187</v>
+        <v>1073</v>
       </c>
       <c r="J41" t="n">
-        <v>1335</v>
+        <v>1203</v>
       </c>
       <c r="K41" t="n">
-        <v>1189</v>
+        <v>980</v>
       </c>
       <c r="L41" t="n">
-        <v>1122.2</v>
+        <v>1113.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1047</v>
+        <v>1064</v>
       </c>
       <c r="C42" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1164</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1006</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1175</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1079</v>
+      </c>
+      <c r="J42" t="n">
         <v>1093</v>
       </c>
-      <c r="D42" t="n">
-        <v>1206</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1181</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1199</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1095</v>
-      </c>
-      <c r="I42" t="n">
-        <v>986</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1072</v>
-      </c>
       <c r="K42" t="n">
-        <v>976</v>
+        <v>1117</v>
       </c>
       <c r="L42" t="n">
-        <v>1105.5</v>
+        <v>1086.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1234</v>
+        <v>1259</v>
       </c>
       <c r="C43" t="n">
-        <v>1108</v>
+        <v>1301</v>
       </c>
       <c r="D43" t="n">
-        <v>1166</v>
+        <v>1137</v>
       </c>
       <c r="E43" t="n">
-        <v>1217</v>
+        <v>1290</v>
       </c>
       <c r="F43" t="n">
-        <v>1027</v>
+        <v>1110</v>
       </c>
       <c r="G43" t="n">
-        <v>1330</v>
+        <v>1292</v>
       </c>
       <c r="H43" t="n">
-        <v>1203</v>
+        <v>1068</v>
       </c>
       <c r="I43" t="n">
-        <v>1076</v>
+        <v>1280</v>
       </c>
       <c r="J43" t="n">
-        <v>956</v>
+        <v>1093</v>
       </c>
       <c r="K43" t="n">
-        <v>1247</v>
+        <v>1121</v>
       </c>
       <c r="L43" t="n">
-        <v>1156.4</v>
+        <v>1195.1</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1337</v>
+        <v>1065</v>
       </c>
       <c r="C44" t="n">
-        <v>1109</v>
+        <v>1134</v>
       </c>
       <c r="D44" t="n">
-        <v>1010</v>
+        <v>1148</v>
       </c>
       <c r="E44" t="n">
+        <v>1062</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1258</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1070</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1061</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1142</v>
+      </c>
+      <c r="J44" t="n">
         <v>1231</v>
       </c>
-      <c r="F44" t="n">
-        <v>1238</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1322</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1203</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1126</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1218</v>
-      </c>
       <c r="K44" t="n">
-        <v>1128</v>
+        <v>1390</v>
       </c>
       <c r="L44" t="n">
-        <v>1192.2</v>
+        <v>1156.1</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1098</v>
+        <v>1000</v>
       </c>
       <c r="C45" t="n">
-        <v>1246</v>
+        <v>1083</v>
       </c>
       <c r="D45" t="n">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="E45" t="n">
-        <v>1154</v>
+        <v>1141</v>
       </c>
       <c r="F45" t="n">
-        <v>1002</v>
+        <v>1106</v>
       </c>
       <c r="G45" t="n">
-        <v>1228</v>
+        <v>1058</v>
       </c>
       <c r="H45" t="n">
-        <v>1071</v>
+        <v>1162</v>
       </c>
       <c r="I45" t="n">
-        <v>1339</v>
+        <v>1085</v>
       </c>
       <c r="J45" t="n">
-        <v>1047</v>
+        <v>1110</v>
       </c>
       <c r="K45" t="n">
-        <v>1067</v>
+        <v>1183</v>
       </c>
       <c r="L45" t="n">
-        <v>1131.4</v>
+        <v>1097.8</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1197</v>
+        <v>1305</v>
       </c>
       <c r="C46" t="n">
-        <v>1107</v>
+        <v>1319</v>
       </c>
       <c r="D46" t="n">
-        <v>1074</v>
+        <v>1283</v>
       </c>
       <c r="E46" t="n">
-        <v>1095</v>
+        <v>1359</v>
       </c>
       <c r="F46" t="n">
-        <v>1100</v>
+        <v>1258</v>
       </c>
       <c r="G46" t="n">
-        <v>1352</v>
+        <v>1212</v>
       </c>
       <c r="H46" t="n">
-        <v>1240</v>
+        <v>1213</v>
       </c>
       <c r="I46" t="n">
-        <v>1141</v>
+        <v>1038</v>
       </c>
       <c r="J46" t="n">
-        <v>1252</v>
+        <v>1044</v>
       </c>
       <c r="K46" t="n">
-        <v>1285</v>
+        <v>1055</v>
       </c>
       <c r="L46" t="n">
-        <v>1184.3</v>
+        <v>1208.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="C47" t="n">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="D47" t="n">
-        <v>1320</v>
+        <v>1483</v>
       </c>
       <c r="E47" t="n">
-        <v>1426</v>
+        <v>1086</v>
       </c>
       <c r="F47" t="n">
-        <v>1184</v>
+        <v>1207</v>
       </c>
       <c r="G47" t="n">
-        <v>1323</v>
+        <v>961</v>
       </c>
       <c r="H47" t="n">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="I47" t="n">
-        <v>1176</v>
+        <v>1139</v>
       </c>
       <c r="J47" t="n">
-        <v>1137</v>
+        <v>1182</v>
       </c>
       <c r="K47" t="n">
-        <v>1234</v>
+        <v>1191</v>
       </c>
       <c r="L47" t="n">
-        <v>1235.6</v>
+        <v>1183.9</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1214</v>
+        <v>1064</v>
       </c>
       <c r="C48" t="n">
-        <v>1093</v>
+        <v>1213</v>
       </c>
       <c r="D48" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F48" t="n">
         <v>1143</v>
       </c>
-      <c r="E48" t="n">
-        <v>1125</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1075</v>
-      </c>
       <c r="G48" t="n">
-        <v>1174</v>
+        <v>1248</v>
       </c>
       <c r="H48" t="n">
-        <v>1087</v>
+        <v>1137</v>
       </c>
       <c r="I48" t="n">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="J48" t="n">
-        <v>1085</v>
+        <v>1168</v>
       </c>
       <c r="K48" t="n">
-        <v>1078</v>
+        <v>1159</v>
       </c>
       <c r="L48" t="n">
-        <v>1120.8</v>
+        <v>1152.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1135</v>
+        <v>936</v>
       </c>
       <c r="C49" t="n">
-        <v>1273</v>
+        <v>1042</v>
       </c>
       <c r="D49" t="n">
-        <v>1050</v>
+        <v>1302</v>
       </c>
       <c r="E49" t="n">
-        <v>1068</v>
+        <v>993</v>
       </c>
       <c r="F49" t="n">
-        <v>1162</v>
+        <v>1109</v>
       </c>
       <c r="G49" t="n">
-        <v>1078</v>
+        <v>1194</v>
       </c>
       <c r="H49" t="n">
-        <v>1075</v>
+        <v>1156</v>
       </c>
       <c r="I49" t="n">
-        <v>1164</v>
+        <v>1103</v>
       </c>
       <c r="J49" t="n">
-        <v>1112</v>
+        <v>1134</v>
       </c>
       <c r="K49" t="n">
-        <v>1175</v>
+        <v>1003</v>
       </c>
       <c r="L49" t="n">
-        <v>1129.2</v>
+        <v>1097.2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1014</v>
+        <v>1043</v>
       </c>
       <c r="C50" t="n">
-        <v>1050</v>
+        <v>1212</v>
       </c>
       <c r="D50" t="n">
-        <v>1064</v>
+        <v>957</v>
       </c>
       <c r="E50" t="n">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="F50" t="n">
-        <v>1120</v>
+        <v>1025</v>
       </c>
       <c r="G50" t="n">
-        <v>1129</v>
+        <v>1101</v>
       </c>
       <c r="H50" t="n">
-        <v>1138</v>
+        <v>1057</v>
       </c>
       <c r="I50" t="n">
-        <v>1099</v>
+        <v>1161</v>
       </c>
       <c r="J50" t="n">
-        <v>966</v>
+        <v>1060</v>
       </c>
       <c r="K50" t="n">
-        <v>1116</v>
+        <v>1038</v>
       </c>
       <c r="L50" t="n">
-        <v>1072</v>
+        <v>1069.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1034</v>
+        <v>984</v>
       </c>
       <c r="C51" t="n">
-        <v>1045</v>
+        <v>1169</v>
       </c>
       <c r="D51" t="n">
-        <v>1036</v>
+        <v>1197</v>
       </c>
       <c r="E51" t="n">
-        <v>1100</v>
+        <v>1089</v>
       </c>
       <c r="F51" t="n">
-        <v>1057</v>
+        <v>1191</v>
       </c>
       <c r="G51" t="n">
-        <v>981</v>
+        <v>1128</v>
       </c>
       <c r="H51" t="n">
-        <v>1067</v>
+        <v>1044</v>
       </c>
       <c r="I51" t="n">
-        <v>963</v>
+        <v>1094</v>
       </c>
       <c r="J51" t="n">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="K51" t="n">
-        <v>1007</v>
+        <v>1072</v>
       </c>
       <c r="L51" t="n">
-        <v>1043.3</v>
+        <v>1111.9</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1162.18</v>
+        <v>1152.52</v>
       </c>
       <c r="C52" t="n">
-        <v>1136.78</v>
+        <v>1149.5</v>
       </c>
       <c r="D52" t="n">
-        <v>1128.16</v>
+        <v>1133.64</v>
       </c>
       <c r="E52" t="n">
-        <v>1162.38</v>
+        <v>1123.68</v>
       </c>
       <c r="F52" t="n">
-        <v>1107.72</v>
+        <v>1138.44</v>
       </c>
       <c r="G52" t="n">
-        <v>1143.04</v>
+        <v>1118.7</v>
       </c>
       <c r="H52" t="n">
-        <v>1152.78</v>
+        <v>1138.92</v>
       </c>
       <c r="I52" t="n">
-        <v>1155.22</v>
+        <v>1143.18</v>
       </c>
       <c r="J52" t="n">
-        <v>1148.32</v>
+        <v>1116.82</v>
       </c>
       <c r="K52" t="n">
-        <v>1130.94</v>
+        <v>1151.96</v>
       </c>
       <c r="L52" t="n">
-        <v>1142.752</v>
+        <v>1136.736</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12.80548429489136</v>
+        <v>13.15298080444336</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73960185050964</v>
+        <v>17.07746934890747</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6857476234436</v>
+        <v>16.55104517936707</v>
       </c>
       <c r="E2" t="n">
-        <v>11.81494188308716</v>
+        <v>14.47113060951233</v>
       </c>
       <c r="F2" t="n">
-        <v>11.68628573417664</v>
+        <v>12.63982605934143</v>
       </c>
       <c r="G2" t="n">
-        <v>12.10931611061096</v>
+        <v>12.59690141677856</v>
       </c>
       <c r="H2" t="n">
-        <v>11.71167850494385</v>
+        <v>13.30364108085632</v>
       </c>
       <c r="I2" t="n">
-        <v>14.1564519405365</v>
+        <v>12.8532509803772</v>
       </c>
       <c r="J2" t="n">
-        <v>12.91664886474609</v>
+        <v>12.53657054901123</v>
       </c>
       <c r="K2" t="n">
-        <v>14.06803369522095</v>
+        <v>12.8063952922821</v>
       </c>
       <c r="L2" t="n">
-        <v>12.66941905021667</v>
+        <v>13.79892113208771</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>13.65636110305786</v>
+        <v>16.38227081298828</v>
       </c>
       <c r="C3" t="n">
-        <v>12.64790606498718</v>
+        <v>11.36853289604187</v>
       </c>
       <c r="D3" t="n">
-        <v>11.40692687034607</v>
+        <v>12.45326948165894</v>
       </c>
       <c r="E3" t="n">
-        <v>14.9304518699646</v>
+        <v>11.70865058898926</v>
       </c>
       <c r="F3" t="n">
-        <v>11.72566652297974</v>
+        <v>12.00043082237244</v>
       </c>
       <c r="G3" t="n">
-        <v>10.71818614006042</v>
+        <v>11.81489610671997</v>
       </c>
       <c r="H3" t="n">
-        <v>10.84636044502258</v>
+        <v>12.4792013168335</v>
       </c>
       <c r="I3" t="n">
-        <v>12.29116988182068</v>
+        <v>15.54985117912292</v>
       </c>
       <c r="J3" t="n">
-        <v>11.98793816566467</v>
+        <v>11.50715780258179</v>
       </c>
       <c r="K3" t="n">
-        <v>10.61894059181213</v>
+        <v>12.16798877716064</v>
       </c>
       <c r="L3" t="n">
-        <v>12.08299076557159</v>
+        <v>12.74322497844696</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>18.08628749847412</v>
+        <v>14.28762269020081</v>
       </c>
       <c r="C4" t="n">
-        <v>13.99707365036011</v>
+        <v>12.97091960906982</v>
       </c>
       <c r="D4" t="n">
-        <v>15.93101716041565</v>
+        <v>13.4767119884491</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02408504486084</v>
+        <v>12.9036602973938</v>
       </c>
       <c r="F4" t="n">
-        <v>12.46004605293274</v>
+        <v>13.1719377040863</v>
       </c>
       <c r="G4" t="n">
-        <v>16.2826144695282</v>
+        <v>13.97540783882141</v>
       </c>
       <c r="H4" t="n">
-        <v>12.61816954612732</v>
+        <v>12.77396845817566</v>
       </c>
       <c r="I4" t="n">
-        <v>13.91731142997742</v>
+        <v>13.05480670928955</v>
       </c>
       <c r="J4" t="n">
-        <v>17.94120240211487</v>
+        <v>13.00574398040771</v>
       </c>
       <c r="K4" t="n">
-        <v>18.26343894004822</v>
+        <v>14.17015194892883</v>
       </c>
       <c r="L4" t="n">
-        <v>15.25212461948395</v>
+        <v>13.3790931224823</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>11.51816201210022</v>
+        <v>10.99444317817688</v>
       </c>
       <c r="C5" t="n">
-        <v>10.90969347953796</v>
+        <v>12.34140872955322</v>
       </c>
       <c r="D5" t="n">
-        <v>11.77456855773926</v>
+        <v>11.5742347240448</v>
       </c>
       <c r="E5" t="n">
-        <v>11.32460975646973</v>
+        <v>11.74920320510864</v>
       </c>
       <c r="F5" t="n">
-        <v>11.50927543640137</v>
+        <v>11.9361047744751</v>
       </c>
       <c r="G5" t="n">
-        <v>11.8942186832428</v>
+        <v>11.06830525398254</v>
       </c>
       <c r="H5" t="n">
-        <v>12.40537095069885</v>
+        <v>10.72418189048767</v>
       </c>
       <c r="I5" t="n">
-        <v>11.47397089004517</v>
+        <v>11.7655291557312</v>
       </c>
       <c r="J5" t="n">
-        <v>11.85477113723755</v>
+        <v>12.25976753234863</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5760281085968</v>
+        <v>10.91769027709961</v>
       </c>
       <c r="L5" t="n">
-        <v>11.52406690120697</v>
+        <v>11.53308687210083</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>11.84983086585999</v>
+        <v>17.15380144119263</v>
       </c>
       <c r="C6" t="n">
-        <v>12.08767032623291</v>
+        <v>12.38805294036865</v>
       </c>
       <c r="D6" t="n">
-        <v>16.99618816375732</v>
+        <v>13.25001120567322</v>
       </c>
       <c r="E6" t="n">
-        <v>12.39241528511047</v>
+        <v>11.86716198921204</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80389308929443</v>
+        <v>12.59721040725708</v>
       </c>
       <c r="G6" t="n">
-        <v>13.33948922157288</v>
+        <v>12.83351111412048</v>
       </c>
       <c r="H6" t="n">
-        <v>12.39889597892761</v>
+        <v>11.38447546958923</v>
       </c>
       <c r="I6" t="n">
-        <v>11.56154680252075</v>
+        <v>17.70438146591187</v>
       </c>
       <c r="J6" t="n">
-        <v>17.34225344657898</v>
+        <v>11.74324584007263</v>
       </c>
       <c r="K6" t="n">
-        <v>12.23482608795166</v>
+        <v>13.00588345527649</v>
       </c>
       <c r="L6" t="n">
-        <v>13.2007009267807</v>
+        <v>13.39277353286743</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>14.53944849967957</v>
+        <v>12.67821097373962</v>
       </c>
       <c r="C7" t="n">
-        <v>12.11088991165161</v>
+        <v>11.59193897247314</v>
       </c>
       <c r="D7" t="n">
-        <v>13.06274151802063</v>
+        <v>12.53758502006531</v>
       </c>
       <c r="E7" t="n">
-        <v>12.32703828811646</v>
+        <v>11.8583869934082</v>
       </c>
       <c r="F7" t="n">
-        <v>13.04575324058533</v>
+        <v>12.27971744537354</v>
       </c>
       <c r="G7" t="n">
-        <v>12.57496404647827</v>
+        <v>13.88012957572937</v>
       </c>
       <c r="H7" t="n">
-        <v>12.92256474494934</v>
+        <v>16.90600228309631</v>
       </c>
       <c r="I7" t="n">
-        <v>17.1607038974762</v>
+        <v>11.96488332748413</v>
       </c>
       <c r="J7" t="n">
-        <v>11.93606066703796</v>
+        <v>12.09956383705139</v>
       </c>
       <c r="K7" t="n">
-        <v>11.64630126953125</v>
+        <v>12.51695084571838</v>
       </c>
       <c r="L7" t="n">
-        <v>13.13264660835266</v>
+        <v>12.83133692741394</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.36199831962585</v>
+        <v>12.26610350608826</v>
       </c>
       <c r="C8" t="n">
-        <v>10.90173625946045</v>
+        <v>13.06403970718384</v>
       </c>
       <c r="D8" t="n">
-        <v>12.32510447502136</v>
+        <v>17.35933208465576</v>
       </c>
       <c r="E8" t="n">
-        <v>16.13385033607483</v>
+        <v>11.49018025398254</v>
       </c>
       <c r="F8" t="n">
-        <v>12.51654505729675</v>
+        <v>12.90397167205811</v>
       </c>
       <c r="G8" t="n">
-        <v>14.53648018836975</v>
+        <v>11.55442118644714</v>
       </c>
       <c r="H8" t="n">
-        <v>12.55506300926208</v>
+        <v>14.83741188049316</v>
       </c>
       <c r="I8" t="n">
-        <v>11.79049372673035</v>
+        <v>14.06391954421997</v>
       </c>
       <c r="J8" t="n">
-        <v>11.40591382980347</v>
+        <v>11.76386904716492</v>
       </c>
       <c r="K8" t="n">
-        <v>12.47127461433411</v>
+        <v>15.12913060188293</v>
       </c>
       <c r="L8" t="n">
-        <v>12.6998459815979</v>
+        <v>13.44323794841766</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30014157295227</v>
+        <v>11.84119153022766</v>
       </c>
       <c r="C9" t="n">
-        <v>11.30909657478333</v>
+        <v>12.19927096366882</v>
       </c>
       <c r="D9" t="n">
-        <v>12.97945189476013</v>
+        <v>11.87210822105408</v>
       </c>
       <c r="E9" t="n">
-        <v>12.33149409294128</v>
+        <v>15.32460331916809</v>
       </c>
       <c r="F9" t="n">
-        <v>11.91748309135437</v>
+        <v>10.8632493019104</v>
       </c>
       <c r="G9" t="n">
-        <v>11.62571668624878</v>
+        <v>11.69140768051147</v>
       </c>
       <c r="H9" t="n">
-        <v>12.88066172599792</v>
+        <v>11.97387480735779</v>
       </c>
       <c r="I9" t="n">
-        <v>13.53235006332397</v>
+        <v>12.33445191383362</v>
       </c>
       <c r="J9" t="n">
-        <v>10.50318074226379</v>
+        <v>15.97791051864624</v>
       </c>
       <c r="K9" t="n">
-        <v>12.83962059020996</v>
+        <v>11.8042995929718</v>
       </c>
       <c r="L9" t="n">
-        <v>12.52191970348358</v>
+        <v>12.588236784935</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.05672240257263</v>
+        <v>15.3804624080658</v>
       </c>
       <c r="C10" t="n">
-        <v>13.7993438243866</v>
+        <v>12.25884747505188</v>
       </c>
       <c r="D10" t="n">
-        <v>11.84881591796875</v>
+        <v>12.44392490386963</v>
       </c>
       <c r="E10" t="n">
-        <v>11.01717782020569</v>
+        <v>13.60933709144592</v>
       </c>
       <c r="F10" t="n">
-        <v>12.10219740867615</v>
+        <v>11.85796451568604</v>
       </c>
       <c r="G10" t="n">
-        <v>12.07227778434753</v>
+        <v>12.13262939453125</v>
       </c>
       <c r="H10" t="n">
-        <v>16.43194150924683</v>
+        <v>14.58781123161316</v>
       </c>
       <c r="I10" t="n">
-        <v>12.19636583328247</v>
+        <v>11.87678599357605</v>
       </c>
       <c r="J10" t="n">
-        <v>11.9908390045166</v>
+        <v>12.37545084953308</v>
       </c>
       <c r="K10" t="n">
-        <v>12.53700065612793</v>
+        <v>12.45129203796387</v>
       </c>
       <c r="L10" t="n">
-        <v>12.50526821613312</v>
+        <v>12.89745059013367</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>12.86938261985779</v>
+        <v>12.67767333984375</v>
       </c>
       <c r="C11" t="n">
-        <v>11.73191595077515</v>
+        <v>12.67022323608398</v>
       </c>
       <c r="D11" t="n">
-        <v>11.60319948196411</v>
+        <v>12.95946073532104</v>
       </c>
       <c r="E11" t="n">
-        <v>15.01219582557678</v>
+        <v>15.28156661987305</v>
       </c>
       <c r="F11" t="n">
-        <v>11.61488008499146</v>
+        <v>13.69748091697693</v>
       </c>
       <c r="G11" t="n">
-        <v>12.02829313278198</v>
+        <v>13.86716151237488</v>
       </c>
       <c r="H11" t="n">
-        <v>11.9408905506134</v>
+        <v>12.31764054298401</v>
       </c>
       <c r="I11" t="n">
-        <v>13.11529278755188</v>
+        <v>12.57994890213013</v>
       </c>
       <c r="J11" t="n">
-        <v>17.97997808456421</v>
+        <v>12.33903098106384</v>
       </c>
       <c r="K11" t="n">
-        <v>13.66133451461792</v>
+        <v>12.03141689300537</v>
       </c>
       <c r="L11" t="n">
-        <v>13.15573630332947</v>
+        <v>13.0421603679657</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>12.00380110740662</v>
+        <v>16.94130110740662</v>
       </c>
       <c r="C12" t="n">
-        <v>11.97441983222961</v>
+        <v>14.0746386051178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.28297567367554</v>
+        <v>16.07230949401855</v>
       </c>
       <c r="E12" t="n">
-        <v>15.40449166297913</v>
+        <v>12.77081704139709</v>
       </c>
       <c r="F12" t="n">
-        <v>16.20787501335144</v>
+        <v>12.27805519104004</v>
       </c>
       <c r="G12" t="n">
-        <v>13.05186080932617</v>
+        <v>17.92783284187317</v>
       </c>
       <c r="H12" t="n">
-        <v>12.22694301605225</v>
+        <v>16.54177236557007</v>
       </c>
       <c r="I12" t="n">
-        <v>16.8542115688324</v>
+        <v>15.34458756446838</v>
       </c>
       <c r="J12" t="n">
-        <v>12.84131526947021</v>
+        <v>16.87852430343628</v>
       </c>
       <c r="K12" t="n">
-        <v>14.73507928848267</v>
+        <v>17.52278113365173</v>
       </c>
       <c r="L12" t="n">
-        <v>13.8582973241806</v>
+        <v>15.63526196479797</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>13.69166135787964</v>
+        <v>12.58592391014099</v>
       </c>
       <c r="C13" t="n">
-        <v>13.29672145843506</v>
+        <v>17.36921405792236</v>
       </c>
       <c r="D13" t="n">
-        <v>15.25317406654358</v>
+        <v>18.29638719558716</v>
       </c>
       <c r="E13" t="n">
-        <v>12.45628905296326</v>
+        <v>15.80762124061584</v>
       </c>
       <c r="F13" t="n">
-        <v>17.18658590316772</v>
+        <v>14.76309132575989</v>
       </c>
       <c r="G13" t="n">
-        <v>17.97257924079895</v>
+        <v>13.26332402229309</v>
       </c>
       <c r="H13" t="n">
-        <v>22.69962811470032</v>
+        <v>13.21661686897278</v>
       </c>
       <c r="I13" t="n">
-        <v>21.97724008560181</v>
+        <v>17.03097891807556</v>
       </c>
       <c r="J13" t="n">
-        <v>15.26981544494629</v>
+        <v>13.61979150772095</v>
       </c>
       <c r="K13" t="n">
-        <v>15.69711470603943</v>
+        <v>16.41515517234802</v>
       </c>
       <c r="L13" t="n">
-        <v>16.55008094310761</v>
+        <v>15.23681042194366</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>20.23949885368347</v>
+        <v>12.59843707084656</v>
       </c>
       <c r="C14" t="n">
-        <v>15.14890670776367</v>
+        <v>12.39944124221802</v>
       </c>
       <c r="D14" t="n">
-        <v>14.85255694389343</v>
+        <v>13.7384672164917</v>
       </c>
       <c r="E14" t="n">
-        <v>16.79752039909363</v>
+        <v>13.44181609153748</v>
       </c>
       <c r="F14" t="n">
-        <v>12.89756655693054</v>
+        <v>12.24582409858704</v>
       </c>
       <c r="G14" t="n">
-        <v>14.42772960662842</v>
+        <v>12.34716892242432</v>
       </c>
       <c r="H14" t="n">
-        <v>13.90230464935303</v>
+        <v>16.79715895652771</v>
       </c>
       <c r="I14" t="n">
-        <v>12.91956233978271</v>
+        <v>17.16975212097168</v>
       </c>
       <c r="J14" t="n">
-        <v>17.23125243186951</v>
+        <v>13.63825178146362</v>
       </c>
       <c r="K14" t="n">
-        <v>14.89557194709778</v>
+        <v>13.09016442298889</v>
       </c>
       <c r="L14" t="n">
-        <v>15.33124704360962</v>
+        <v>13.7466481924057</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>12.94388914108276</v>
+        <v>12.5707905292511</v>
       </c>
       <c r="C15" t="n">
-        <v>11.69638442993164</v>
+        <v>12.16485166549683</v>
       </c>
       <c r="D15" t="n">
-        <v>17.96224927902222</v>
+        <v>11.99180364608765</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13695478439331</v>
+        <v>11.56811189651489</v>
       </c>
       <c r="F15" t="n">
-        <v>12.47700548171997</v>
+        <v>11.74149584770203</v>
       </c>
       <c r="G15" t="n">
-        <v>12.39344453811646</v>
+        <v>14.96040511131287</v>
       </c>
       <c r="H15" t="n">
-        <v>12.12769865989685</v>
+        <v>13.1575300693512</v>
       </c>
       <c r="I15" t="n">
-        <v>11.42389345169067</v>
+        <v>12.33163285255432</v>
       </c>
       <c r="J15" t="n">
-        <v>15.39977121353149</v>
+        <v>11.39383673667908</v>
       </c>
       <c r="K15" t="n">
-        <v>12.62014293670654</v>
+        <v>16.46176743507385</v>
       </c>
       <c r="L15" t="n">
-        <v>13.11814339160919</v>
+        <v>12.83422257900238</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>17.14472889900208</v>
+        <v>11.7040331363678</v>
       </c>
       <c r="C16" t="n">
-        <v>13.46043539047241</v>
+        <v>16.1130518913269</v>
       </c>
       <c r="D16" t="n">
-        <v>11.37287259101868</v>
+        <v>11.75812339782715</v>
       </c>
       <c r="E16" t="n">
-        <v>18.20861291885376</v>
+        <v>11.89670419692993</v>
       </c>
       <c r="F16" t="n">
-        <v>14.94360756874084</v>
+        <v>15.49401545524597</v>
       </c>
       <c r="G16" t="n">
-        <v>11.83186340332031</v>
+        <v>12.12861776351929</v>
       </c>
       <c r="H16" t="n">
-        <v>16.43256664276123</v>
+        <v>16.19275236129761</v>
       </c>
       <c r="I16" t="n">
-        <v>19.09135270118713</v>
+        <v>16.82958984375</v>
       </c>
       <c r="J16" t="n">
-        <v>15.0319607257843</v>
+        <v>11.61344528198242</v>
       </c>
       <c r="K16" t="n">
-        <v>11.649822473526</v>
+        <v>14.97381162643433</v>
       </c>
       <c r="L16" t="n">
-        <v>14.91678233146667</v>
+        <v>13.87041449546814</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>12.21015620231628</v>
+        <v>11.8428316116333</v>
       </c>
       <c r="C17" t="n">
-        <v>13.31339263916016</v>
+        <v>12.13357877731323</v>
       </c>
       <c r="D17" t="n">
-        <v>12.82149147987366</v>
+        <v>12.0807056427002</v>
       </c>
       <c r="E17" t="n">
-        <v>14.10169839859009</v>
+        <v>18.22504734992981</v>
       </c>
       <c r="F17" t="n">
-        <v>12.68564701080322</v>
+        <v>12.13259553909302</v>
       </c>
       <c r="G17" t="n">
-        <v>15.60222697257996</v>
+        <v>11.84931254386902</v>
       </c>
       <c r="H17" t="n">
-        <v>11.90715670585632</v>
+        <v>12.70859360694885</v>
       </c>
       <c r="I17" t="n">
-        <v>12.37797451019287</v>
+        <v>11.50816059112549</v>
       </c>
       <c r="J17" t="n">
-        <v>12.70710492134094</v>
+        <v>12.53952097892761</v>
       </c>
       <c r="K17" t="n">
-        <v>12.61983275413513</v>
+        <v>13.56549406051636</v>
       </c>
       <c r="L17" t="n">
-        <v>13.03466815948486</v>
+        <v>12.85858407020569</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>17.37322807312012</v>
+        <v>16.43807697296143</v>
       </c>
       <c r="C18" t="n">
-        <v>15.65707898139954</v>
+        <v>15.53388547897339</v>
       </c>
       <c r="D18" t="n">
-        <v>12.08468985557556</v>
+        <v>11.75726723670959</v>
       </c>
       <c r="E18" t="n">
-        <v>16.08850908279419</v>
+        <v>14.1354820728302</v>
       </c>
       <c r="F18" t="n">
-        <v>12.00091338157654</v>
+        <v>12.45076441764832</v>
       </c>
       <c r="G18" t="n">
-        <v>15.5009605884552</v>
+        <v>11.99493622779846</v>
       </c>
       <c r="H18" t="n">
-        <v>16.56229281425476</v>
+        <v>12.02436184883118</v>
       </c>
       <c r="I18" t="n">
-        <v>16.46998047828674</v>
+        <v>17.99743914604187</v>
       </c>
       <c r="J18" t="n">
-        <v>16.36731648445129</v>
+        <v>13.47892951965332</v>
       </c>
       <c r="K18" t="n">
-        <v>14.14542984962463</v>
+        <v>14.32420754432678</v>
       </c>
       <c r="L18" t="n">
-        <v>15.22503995895386</v>
+        <v>14.01353504657745</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>13.1530613899231</v>
+        <v>14.4036009311676</v>
       </c>
       <c r="C19" t="n">
-        <v>12.28826928138733</v>
+        <v>14.8722996711731</v>
       </c>
       <c r="D19" t="n">
-        <v>13.0188136100769</v>
+        <v>13.60558414459229</v>
       </c>
       <c r="E19" t="n">
-        <v>11.84677982330322</v>
+        <v>14.20005989074707</v>
       </c>
       <c r="F19" t="n">
-        <v>12.31609725952148</v>
+        <v>15.04685258865356</v>
       </c>
       <c r="G19" t="n">
-        <v>12.03234553337097</v>
+        <v>12.64009356498718</v>
       </c>
       <c r="H19" t="n">
-        <v>12.23377776145935</v>
+        <v>15.72507452964783</v>
       </c>
       <c r="I19" t="n">
-        <v>16.93733477592468</v>
+        <v>14.58059883117676</v>
       </c>
       <c r="J19" t="n">
-        <v>17.4085853099823</v>
+        <v>14.43450236320496</v>
       </c>
       <c r="K19" t="n">
-        <v>13.75440859794617</v>
+        <v>14.32723450660706</v>
       </c>
       <c r="L19" t="n">
-        <v>13.49894733428955</v>
+        <v>14.38359010219574</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>15.06457734107971</v>
+        <v>16.70580124855042</v>
       </c>
       <c r="C20" t="n">
-        <v>13.6667115688324</v>
+        <v>13.20631217956543</v>
       </c>
       <c r="D20" t="n">
-        <v>11.8890016078949</v>
+        <v>11.75860643386841</v>
       </c>
       <c r="E20" t="n">
-        <v>11.55240821838379</v>
+        <v>12.15928149223328</v>
       </c>
       <c r="F20" t="n">
-        <v>11.10556530952454</v>
+        <v>15.3306291103363</v>
       </c>
       <c r="G20" t="n">
-        <v>11.27715110778809</v>
+        <v>13.28489828109741</v>
       </c>
       <c r="H20" t="n">
-        <v>13.05102801322937</v>
+        <v>14.04546284675598</v>
       </c>
       <c r="I20" t="n">
-        <v>11.05820846557617</v>
+        <v>13.73814296722412</v>
       </c>
       <c r="J20" t="n">
-        <v>14.96010804176331</v>
+        <v>16.79720520973206</v>
       </c>
       <c r="K20" t="n">
-        <v>10.87668514251709</v>
+        <v>14.69455361366272</v>
       </c>
       <c r="L20" t="n">
-        <v>12.45014448165893</v>
+        <v>14.17208933830261</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>12.14065933227539</v>
+        <v>11.92909860610962</v>
       </c>
       <c r="C21" t="n">
-        <v>12.22941470146179</v>
+        <v>13.0587363243103</v>
       </c>
       <c r="D21" t="n">
-        <v>12.45179533958435</v>
+        <v>12.48019194602966</v>
       </c>
       <c r="E21" t="n">
-        <v>12.25476336479187</v>
+        <v>11.77501368522644</v>
       </c>
       <c r="F21" t="n">
-        <v>12.63079261779785</v>
+        <v>13.81486034393311</v>
       </c>
       <c r="G21" t="n">
-        <v>16.09197545051575</v>
+        <v>13.64519762992859</v>
       </c>
       <c r="H21" t="n">
-        <v>12.73208737373352</v>
+        <v>11.97295880317688</v>
       </c>
       <c r="I21" t="n">
-        <v>12.59585452079773</v>
+        <v>12.11466217041016</v>
       </c>
       <c r="J21" t="n">
-        <v>12.37293219566345</v>
+        <v>11.80391407012939</v>
       </c>
       <c r="K21" t="n">
-        <v>12.17200398445129</v>
+        <v>11.63336586952209</v>
       </c>
       <c r="L21" t="n">
-        <v>12.7672278881073</v>
+        <v>12.42279994487762</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>16.39228224754333</v>
+        <v>13.46639728546143</v>
       </c>
       <c r="C22" t="n">
-        <v>13.19283890724182</v>
+        <v>12.17281866073608</v>
       </c>
       <c r="D22" t="n">
-        <v>12.18491625785828</v>
+        <v>16.74596238136292</v>
       </c>
       <c r="E22" t="n">
-        <v>15.1967658996582</v>
+        <v>12.37440204620361</v>
       </c>
       <c r="F22" t="n">
-        <v>11.99740195274353</v>
+        <v>13.09293627738953</v>
       </c>
       <c r="G22" t="n">
-        <v>12.12857222557068</v>
+        <v>16.78531908988953</v>
       </c>
       <c r="H22" t="n">
-        <v>12.4612398147583</v>
+        <v>13.42652058601379</v>
       </c>
       <c r="I22" t="n">
-        <v>13.55024552345276</v>
+        <v>13.24926519393921</v>
       </c>
       <c r="J22" t="n">
-        <v>13.37108135223389</v>
+        <v>13.05673742294312</v>
       </c>
       <c r="K22" t="n">
-        <v>13.01521325111389</v>
+        <v>13.62029886245728</v>
       </c>
       <c r="L22" t="n">
-        <v>13.34905574321747</v>
+        <v>13.79906578063965</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>16.02931690216064</v>
+        <v>15.1478750705719</v>
       </c>
       <c r="C23" t="n">
-        <v>10.52613115310669</v>
+        <v>12.82933974266052</v>
       </c>
       <c r="D23" t="n">
-        <v>10.63034772872925</v>
+        <v>14.52149128913879</v>
       </c>
       <c r="E23" t="n">
-        <v>14.72723317146301</v>
+        <v>11.95104742050171</v>
       </c>
       <c r="F23" t="n">
-        <v>14.53974103927612</v>
+        <v>11.845370054245</v>
       </c>
       <c r="G23" t="n">
-        <v>10.37163615226746</v>
+        <v>15.9499032497406</v>
       </c>
       <c r="H23" t="n">
-        <v>10.62737846374512</v>
+        <v>15.46663618087769</v>
       </c>
       <c r="I23" t="n">
-        <v>15.50721073150635</v>
+        <v>12.37943196296692</v>
       </c>
       <c r="J23" t="n">
-        <v>11.71209406852722</v>
+        <v>11.01345086097717</v>
       </c>
       <c r="K23" t="n">
-        <v>11.37500333786011</v>
+        <v>15.50800681114197</v>
       </c>
       <c r="L23" t="n">
-        <v>12.6046092748642</v>
+        <v>13.66125526428223</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>12.03773331642151</v>
+        <v>12.94903683662415</v>
       </c>
       <c r="C24" t="n">
-        <v>13.10492300987244</v>
+        <v>13.6851270198822</v>
       </c>
       <c r="D24" t="n">
-        <v>12.05415010452271</v>
+        <v>12.89862656593323</v>
       </c>
       <c r="E24" t="n">
-        <v>16.49608087539673</v>
+        <v>13.59352493286133</v>
       </c>
       <c r="F24" t="n">
-        <v>15.2407751083374</v>
+        <v>12.99823069572449</v>
       </c>
       <c r="G24" t="n">
-        <v>14.18090987205505</v>
+        <v>13.42687773704529</v>
       </c>
       <c r="H24" t="n">
-        <v>11.83687829971313</v>
+        <v>14.81627321243286</v>
       </c>
       <c r="I24" t="n">
-        <v>13.80790424346924</v>
+        <v>13.10021662712097</v>
       </c>
       <c r="J24" t="n">
-        <v>11.69693994522095</v>
+        <v>12.72706961631775</v>
       </c>
       <c r="K24" t="n">
-        <v>12.69224619865417</v>
+        <v>12.45726418495178</v>
       </c>
       <c r="L24" t="n">
-        <v>13.31485409736633</v>
+        <v>13.26522474288941</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>12.73706150054932</v>
+        <v>17.76476550102234</v>
       </c>
       <c r="C25" t="n">
-        <v>12.93252801895142</v>
+        <v>14.92699027061462</v>
       </c>
       <c r="D25" t="n">
-        <v>15.74939799308777</v>
+        <v>14.38748073577881</v>
       </c>
       <c r="E25" t="n">
-        <v>14.41951513290405</v>
+        <v>14.30817627906799</v>
       </c>
       <c r="F25" t="n">
-        <v>14.06050205230713</v>
+        <v>17.39520716667175</v>
       </c>
       <c r="G25" t="n">
-        <v>16.83820486068726</v>
+        <v>14.3012056350708</v>
       </c>
       <c r="H25" t="n">
-        <v>17.18548202514648</v>
+        <v>20.00631308555603</v>
       </c>
       <c r="I25" t="n">
-        <v>17.26227474212646</v>
+        <v>15.10266089439392</v>
       </c>
       <c r="J25" t="n">
-        <v>16.88019061088562</v>
+        <v>17.42077445983887</v>
       </c>
       <c r="K25" t="n">
-        <v>17.61054182052612</v>
+        <v>17.02381491661072</v>
       </c>
       <c r="L25" t="n">
-        <v>15.56756987571716</v>
+        <v>16.26373889446258</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>10.89563536643982</v>
+        <v>12.23501110076904</v>
       </c>
       <c r="C26" t="n">
-        <v>10.41387939453125</v>
+        <v>12.51225996017456</v>
       </c>
       <c r="D26" t="n">
-        <v>14.30431222915649</v>
+        <v>12.48880386352539</v>
       </c>
       <c r="E26" t="n">
-        <v>11.69610595703125</v>
+        <v>12.85328960418701</v>
       </c>
       <c r="F26" t="n">
-        <v>12.56792163848877</v>
+        <v>11.30772924423218</v>
       </c>
       <c r="G26" t="n">
-        <v>11.57096791267395</v>
+        <v>10.6982696056366</v>
       </c>
       <c r="H26" t="n">
-        <v>16.46450710296631</v>
+        <v>11.10220313072205</v>
       </c>
       <c r="I26" t="n">
-        <v>15.18179130554199</v>
+        <v>10.47430849075317</v>
       </c>
       <c r="J26" t="n">
-        <v>13.05570244789124</v>
+        <v>11.2603075504303</v>
       </c>
       <c r="K26" t="n">
-        <v>10.54916548728943</v>
+        <v>11.51314735412598</v>
       </c>
       <c r="L26" t="n">
-        <v>12.66999888420105</v>
+        <v>11.64453299045563</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>18.6080687046051</v>
+        <v>12.85622453689575</v>
       </c>
       <c r="C27" t="n">
-        <v>12.60884714126587</v>
+        <v>13.13901162147522</v>
       </c>
       <c r="D27" t="n">
-        <v>12.21888661384583</v>
+        <v>12.39041566848755</v>
       </c>
       <c r="E27" t="n">
-        <v>13.88133525848389</v>
+        <v>18.59907150268555</v>
       </c>
       <c r="F27" t="n">
-        <v>13.20470643043518</v>
+        <v>19.26390385627747</v>
       </c>
       <c r="G27" t="n">
-        <v>13.10114550590515</v>
+        <v>12.47673654556274</v>
       </c>
       <c r="H27" t="n">
-        <v>13.57695579528809</v>
+        <v>15.23055243492126</v>
       </c>
       <c r="I27" t="n">
-        <v>12.96001029014587</v>
+        <v>12.23117327690125</v>
       </c>
       <c r="J27" t="n">
-        <v>14.32357931137085</v>
+        <v>13.28438591957092</v>
       </c>
       <c r="K27" t="n">
-        <v>15.02924013137817</v>
+        <v>12.17298245429993</v>
       </c>
       <c r="L27" t="n">
-        <v>13.9512775182724</v>
+        <v>14.16444578170776</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>14.52079391479492</v>
+        <v>11.90318012237549</v>
       </c>
       <c r="C28" t="n">
-        <v>15.61005520820618</v>
+        <v>16.45949363708496</v>
       </c>
       <c r="D28" t="n">
-        <v>11.81498312950134</v>
+        <v>14.37511777877808</v>
       </c>
       <c r="E28" t="n">
-        <v>17.30928015708923</v>
+        <v>11.13155245780945</v>
       </c>
       <c r="F28" t="n">
-        <v>15.49747538566589</v>
+        <v>13.18370485305786</v>
       </c>
       <c r="G28" t="n">
-        <v>14.19150280952454</v>
+        <v>12.11698222160339</v>
       </c>
       <c r="H28" t="n">
-        <v>14.14461302757263</v>
+        <v>11.60942316055298</v>
       </c>
       <c r="I28" t="n">
-        <v>18.9295072555542</v>
+        <v>11.60387706756592</v>
       </c>
       <c r="J28" t="n">
-        <v>17.88574194908142</v>
+        <v>11.72315430641174</v>
       </c>
       <c r="K28" t="n">
-        <v>14.56507325172424</v>
+        <v>14.04148864746094</v>
       </c>
       <c r="L28" t="n">
-        <v>15.44690260887146</v>
+        <v>12.81479742527008</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>12.04843258857727</v>
+        <v>10.84874892234802</v>
       </c>
       <c r="C29" t="n">
-        <v>12.29621171951294</v>
+        <v>16.06817364692688</v>
       </c>
       <c r="D29" t="n">
-        <v>11.68620419502258</v>
+        <v>10.54662847518921</v>
       </c>
       <c r="E29" t="n">
-        <v>13.65078806877136</v>
+        <v>10.92467737197876</v>
       </c>
       <c r="F29" t="n">
-        <v>12.16460180282593</v>
+        <v>11.49720501899719</v>
       </c>
       <c r="G29" t="n">
-        <v>13.96313071250916</v>
+        <v>11.23338723182678</v>
       </c>
       <c r="H29" t="n">
-        <v>16.96787929534912</v>
+        <v>11.32264971733093</v>
       </c>
       <c r="I29" t="n">
-        <v>12.00110721588135</v>
+        <v>11.93210434913635</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28226947784424</v>
+        <v>11.49727177619934</v>
       </c>
       <c r="K29" t="n">
-        <v>14.26808667182922</v>
+        <v>12.92556595802307</v>
       </c>
       <c r="L29" t="n">
-        <v>13.83287117481232</v>
+        <v>11.87964124679565</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>14.9009530544281</v>
+        <v>12.45326662063599</v>
       </c>
       <c r="C30" t="n">
-        <v>14.66755127906799</v>
+        <v>12.58491730690002</v>
       </c>
       <c r="D30" t="n">
-        <v>16.69067239761353</v>
+        <v>15.22772765159607</v>
       </c>
       <c r="E30" t="n">
-        <v>15.24443316459656</v>
+        <v>11.56653475761414</v>
       </c>
       <c r="F30" t="n">
-        <v>14.52293109893799</v>
+        <v>12.24515056610107</v>
       </c>
       <c r="G30" t="n">
-        <v>16.63797545433044</v>
+        <v>12.99425387382507</v>
       </c>
       <c r="H30" t="n">
-        <v>12.67407703399658</v>
+        <v>12.68920469284058</v>
       </c>
       <c r="I30" t="n">
-        <v>17.53401494026184</v>
+        <v>12.26581168174744</v>
       </c>
       <c r="J30" t="n">
-        <v>14.77479934692383</v>
+        <v>17.14791417121887</v>
       </c>
       <c r="K30" t="n">
-        <v>14.88392853736877</v>
+        <v>17.03562235832214</v>
       </c>
       <c r="L30" t="n">
-        <v>15.25313363075256</v>
+        <v>13.62104036808014</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>19.43365883827209</v>
+        <v>15.47113847732544</v>
       </c>
       <c r="C31" t="n">
-        <v>14.62452697753906</v>
+        <v>13.79643368721008</v>
       </c>
       <c r="D31" t="n">
-        <v>12.96826171875</v>
+        <v>12.91753435134888</v>
       </c>
       <c r="E31" t="n">
-        <v>12.46454238891602</v>
+        <v>12.08872866630554</v>
       </c>
       <c r="F31" t="n">
-        <v>12.3014669418335</v>
+        <v>15.34139442443848</v>
       </c>
       <c r="G31" t="n">
-        <v>11.85811710357666</v>
+        <v>15.09657859802246</v>
       </c>
       <c r="H31" t="n">
-        <v>17.90948891639709</v>
+        <v>14.7045726776123</v>
       </c>
       <c r="I31" t="n">
-        <v>13.66414189338684</v>
+        <v>13.10008263587952</v>
       </c>
       <c r="J31" t="n">
-        <v>12.52360391616821</v>
+        <v>12.08922696113586</v>
       </c>
       <c r="K31" t="n">
-        <v>13.06266665458679</v>
+        <v>12.20792245864868</v>
       </c>
       <c r="L31" t="n">
-        <v>14.08104753494263</v>
+        <v>13.68136129379272</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>12.10050296783447</v>
+        <v>11.88132286071777</v>
       </c>
       <c r="C32" t="n">
-        <v>21.57274413108826</v>
+        <v>13.59889578819275</v>
       </c>
       <c r="D32" t="n">
-        <v>16.96866893768311</v>
+        <v>11.91414761543274</v>
       </c>
       <c r="E32" t="n">
-        <v>17.00146460533142</v>
+        <v>12.4783239364624</v>
       </c>
       <c r="F32" t="n">
-        <v>14.21380352973938</v>
+        <v>14.09135985374451</v>
       </c>
       <c r="G32" t="n">
-        <v>13.50943875312805</v>
+        <v>11.49759578704834</v>
       </c>
       <c r="H32" t="n">
-        <v>13.98757481575012</v>
+        <v>12.97273254394531</v>
       </c>
       <c r="I32" t="n">
-        <v>13.61152648925781</v>
+        <v>11.86270952224731</v>
       </c>
       <c r="J32" t="n">
-        <v>13.58968329429626</v>
+        <v>12.3860342502594</v>
       </c>
       <c r="K32" t="n">
-        <v>11.51850724220276</v>
+        <v>16.78722238540649</v>
       </c>
       <c r="L32" t="n">
-        <v>14.80739147663116</v>
+        <v>12.9470344543457</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>13.11831164360046</v>
+        <v>15.04670143127441</v>
       </c>
       <c r="C33" t="n">
-        <v>13.0326030254364</v>
+        <v>13.10618543624878</v>
       </c>
       <c r="D33" t="n">
-        <v>12.41739273071289</v>
+        <v>13.24425363540649</v>
       </c>
       <c r="E33" t="n">
-        <v>13.31060266494751</v>
+        <v>11.39695954322815</v>
       </c>
       <c r="F33" t="n">
-        <v>14.02777099609375</v>
+        <v>12.80673408508301</v>
       </c>
       <c r="G33" t="n">
-        <v>12.39444017410278</v>
+        <v>16.02714538574219</v>
       </c>
       <c r="H33" t="n">
-        <v>14.66472339630127</v>
+        <v>12.93258452415466</v>
       </c>
       <c r="I33" t="n">
-        <v>12.15410923957825</v>
+        <v>12.45829391479492</v>
       </c>
       <c r="J33" t="n">
-        <v>11.92421460151672</v>
+        <v>15.54855036735535</v>
       </c>
       <c r="K33" t="n">
-        <v>14.24968767166138</v>
+        <v>18.99953961372375</v>
       </c>
       <c r="L33" t="n">
-        <v>13.12938561439514</v>
+        <v>14.15669479370117</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>11.89417362213135</v>
+        <v>17.37426066398621</v>
       </c>
       <c r="C34" t="n">
-        <v>12.49914455413818</v>
+        <v>10.55103635787964</v>
       </c>
       <c r="D34" t="n">
-        <v>12.82629871368408</v>
+        <v>11.78335332870483</v>
       </c>
       <c r="E34" t="n">
-        <v>11.81588888168335</v>
+        <v>14.53662610054016</v>
       </c>
       <c r="F34" t="n">
-        <v>11.49913930892944</v>
+        <v>12.44662070274353</v>
       </c>
       <c r="G34" t="n">
-        <v>18.28637599945068</v>
+        <v>11.2691638469696</v>
       </c>
       <c r="H34" t="n">
-        <v>14.62874388694763</v>
+        <v>11.18546485900879</v>
       </c>
       <c r="I34" t="n">
-        <v>13.58647322654724</v>
+        <v>14.95164823532104</v>
       </c>
       <c r="J34" t="n">
-        <v>11.40590667724609</v>
+        <v>11.89558219909668</v>
       </c>
       <c r="K34" t="n">
-        <v>16.49198198318481</v>
+        <v>15.5996515750885</v>
       </c>
       <c r="L34" t="n">
-        <v>13.49341268539429</v>
+        <v>13.1593407869339</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>12.20587205886841</v>
+        <v>12.05529379844666</v>
       </c>
       <c r="C35" t="n">
-        <v>13.12107586860657</v>
+        <v>12.4862334728241</v>
       </c>
       <c r="D35" t="n">
-        <v>13.16644597053528</v>
+        <v>12.23214507102966</v>
       </c>
       <c r="E35" t="n">
-        <v>13.54700231552124</v>
+        <v>12.00274085998535</v>
       </c>
       <c r="F35" t="n">
-        <v>12.58692145347595</v>
+        <v>16.74791193008423</v>
       </c>
       <c r="G35" t="n">
-        <v>11.76749014854431</v>
+        <v>12.72841262817383</v>
       </c>
       <c r="H35" t="n">
-        <v>11.84432196617126</v>
+        <v>13.2724986076355</v>
       </c>
       <c r="I35" t="n">
-        <v>14.08307504653931</v>
+        <v>12.11897993087769</v>
       </c>
       <c r="J35" t="n">
-        <v>13.0407702922821</v>
+        <v>11.94840168952942</v>
       </c>
       <c r="K35" t="n">
-        <v>12.54160642623901</v>
+        <v>12.65244793891907</v>
       </c>
       <c r="L35" t="n">
-        <v>12.79045815467834</v>
+        <v>12.82450659275055</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>12.88319134712219</v>
+        <v>15.42474222183228</v>
       </c>
       <c r="C36" t="n">
-        <v>11.93307781219482</v>
+        <v>12.159512758255</v>
       </c>
       <c r="D36" t="n">
-        <v>13.20339941978455</v>
+        <v>13.73254895210266</v>
       </c>
       <c r="E36" t="n">
-        <v>13.04473304748535</v>
+        <v>12.63879036903381</v>
       </c>
       <c r="F36" t="n">
-        <v>16.39628648757935</v>
+        <v>13.69266891479492</v>
       </c>
       <c r="G36" t="n">
-        <v>11.4519157409668</v>
+        <v>13.10914444923401</v>
       </c>
       <c r="H36" t="n">
-        <v>21.75704336166382</v>
+        <v>13.0667462348938</v>
       </c>
       <c r="I36" t="n">
-        <v>13.53144145011902</v>
+        <v>11.96405625343323</v>
       </c>
       <c r="J36" t="n">
-        <v>16.51024699211121</v>
+        <v>12.075758934021</v>
       </c>
       <c r="K36" t="n">
-        <v>18.63889646530151</v>
+        <v>12.84726619720459</v>
       </c>
       <c r="L36" t="n">
-        <v>14.93502321243286</v>
+        <v>13.07112352848053</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>17.96505331993103</v>
+        <v>11.82687425613403</v>
       </c>
       <c r="C37" t="n">
-        <v>17.02206873893738</v>
+        <v>12.07116365432739</v>
       </c>
       <c r="D37" t="n">
-        <v>11.95439457893372</v>
+        <v>12.63712072372437</v>
       </c>
       <c r="E37" t="n">
-        <v>14.96880650520325</v>
+        <v>11.79531574249268</v>
       </c>
       <c r="F37" t="n">
-        <v>12.86944198608398</v>
+        <v>14.30827879905701</v>
       </c>
       <c r="G37" t="n">
-        <v>11.78636050224304</v>
+        <v>11.59390115737915</v>
       </c>
       <c r="H37" t="n">
-        <v>11.94609308242798</v>
+        <v>14.61545467376709</v>
       </c>
       <c r="I37" t="n">
-        <v>11.93464040756226</v>
+        <v>14.77653241157532</v>
       </c>
       <c r="J37" t="n">
-        <v>11.89576959609985</v>
+        <v>14.0734965801239</v>
       </c>
       <c r="K37" t="n">
-        <v>12.56356954574585</v>
+        <v>16.63744854927063</v>
       </c>
       <c r="L37" t="n">
-        <v>13.49061982631683</v>
+        <v>13.43355865478516</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.11661386489868</v>
+        <v>18.73072552680969</v>
       </c>
       <c r="C38" t="n">
-        <v>11.99882102012634</v>
+        <v>13.13713121414185</v>
       </c>
       <c r="D38" t="n">
-        <v>14.92459416389465</v>
+        <v>12.49265956878662</v>
       </c>
       <c r="E38" t="n">
-        <v>12.27433633804321</v>
+        <v>13.06475162506104</v>
       </c>
       <c r="F38" t="n">
-        <v>12.45475840568542</v>
+        <v>11.87526273727417</v>
       </c>
       <c r="G38" t="n">
-        <v>18.33705592155457</v>
+        <v>12.43929028511047</v>
       </c>
       <c r="H38" t="n">
-        <v>17.25152158737183</v>
+        <v>17.02165627479553</v>
       </c>
       <c r="I38" t="n">
-        <v>12.52991247177124</v>
+        <v>11.90120363235474</v>
       </c>
       <c r="J38" t="n">
-        <v>13.91359114646912</v>
+        <v>12.1031756401062</v>
       </c>
       <c r="K38" t="n">
-        <v>12.79499650001526</v>
+        <v>12.41635060310364</v>
       </c>
       <c r="L38" t="n">
-        <v>13.75962014198303</v>
+        <v>13.5182207107544</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>13.61856746673584</v>
+        <v>11.12914419174194</v>
       </c>
       <c r="C39" t="n">
-        <v>13.7866005897522</v>
+        <v>14.43824124336243</v>
       </c>
       <c r="D39" t="n">
-        <v>10.02488875389099</v>
+        <v>10.63342237472534</v>
       </c>
       <c r="E39" t="n">
-        <v>11.50831699371338</v>
+        <v>10.44738054275513</v>
       </c>
       <c r="F39" t="n">
-        <v>11.67674422264099</v>
+        <v>11.59397006034851</v>
       </c>
       <c r="G39" t="n">
-        <v>10.71466708183289</v>
+        <v>11.2154233455658</v>
       </c>
       <c r="H39" t="n">
-        <v>12.97325706481934</v>
+        <v>11.27477335929871</v>
       </c>
       <c r="I39" t="n">
-        <v>12.38587188720703</v>
+        <v>11.20046710968018</v>
       </c>
       <c r="J39" t="n">
-        <v>12.98695206642151</v>
+        <v>13.76843810081482</v>
       </c>
       <c r="K39" t="n">
-        <v>14.01169514656067</v>
+        <v>11.06479215621948</v>
       </c>
       <c r="L39" t="n">
-        <v>12.36875612735748</v>
+        <v>11.67660524845123</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>15.85688424110413</v>
+        <v>15.10147929191589</v>
       </c>
       <c r="C40" t="n">
-        <v>14.34436798095703</v>
+        <v>12.92489504814148</v>
       </c>
       <c r="D40" t="n">
-        <v>17.51987504959106</v>
+        <v>13.07552528381348</v>
       </c>
       <c r="E40" t="n">
-        <v>13.95195746421814</v>
+        <v>13.12441062927246</v>
       </c>
       <c r="F40" t="n">
-        <v>13.93655300140381</v>
+        <v>13.79058527946472</v>
       </c>
       <c r="G40" t="n">
-        <v>19.4287965297699</v>
+        <v>13.53428530693054</v>
       </c>
       <c r="H40" t="n">
-        <v>17.14125514030457</v>
+        <v>12.15288734436035</v>
       </c>
       <c r="I40" t="n">
-        <v>15.50921154022217</v>
+        <v>13.70188045501709</v>
       </c>
       <c r="J40" t="n">
-        <v>15.94614720344543</v>
+        <v>13.8097071647644</v>
       </c>
       <c r="K40" t="n">
-        <v>19.43495512008667</v>
+        <v>13.51610589027405</v>
       </c>
       <c r="L40" t="n">
-        <v>16.30700032711029</v>
+        <v>13.47317616939545</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>12.40302467346191</v>
+        <v>16.08254814147949</v>
       </c>
       <c r="C41" t="n">
-        <v>10.39142203330994</v>
+        <v>13.84872436523438</v>
       </c>
       <c r="D41" t="n">
-        <v>11.63433122634888</v>
+        <v>10.70422220230103</v>
       </c>
       <c r="E41" t="n">
-        <v>13.49526810646057</v>
+        <v>10.691086769104</v>
       </c>
       <c r="F41" t="n">
-        <v>11.68428015708923</v>
+        <v>10.63293147087097</v>
       </c>
       <c r="G41" t="n">
-        <v>17.26806354522705</v>
+        <v>14.93843531608582</v>
       </c>
       <c r="H41" t="n">
-        <v>12.83209538459778</v>
+        <v>14.91866612434387</v>
       </c>
       <c r="I41" t="n">
-        <v>16.37657761573792</v>
+        <v>10.80693483352661</v>
       </c>
       <c r="J41" t="n">
-        <v>18.72753763198853</v>
+        <v>15.47180390357971</v>
       </c>
       <c r="K41" t="n">
-        <v>13.83679580688477</v>
+        <v>11.39285182952881</v>
       </c>
       <c r="L41" t="n">
-        <v>13.86493961811066</v>
+        <v>12.94882049560547</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>14.14193749427795</v>
+        <v>12.28254723548889</v>
       </c>
       <c r="C42" t="n">
-        <v>15.81642913818359</v>
+        <v>12.2820680141449</v>
       </c>
       <c r="D42" t="n">
-        <v>16.2129065990448</v>
+        <v>12.21711540222168</v>
       </c>
       <c r="E42" t="n">
-        <v>20.10516452789307</v>
+        <v>11.51115417480469</v>
       </c>
       <c r="F42" t="n">
-        <v>14.645676612854</v>
+        <v>14.85518860816956</v>
       </c>
       <c r="G42" t="n">
-        <v>14.19233727455139</v>
+        <v>12.77124834060669</v>
       </c>
       <c r="H42" t="n">
-        <v>12.5647497177124</v>
+        <v>12.26054739952087</v>
       </c>
       <c r="I42" t="n">
-        <v>13.38649725914001</v>
+        <v>13.06998825073242</v>
       </c>
       <c r="J42" t="n">
-        <v>14.00957918167114</v>
+        <v>12.46806716918945</v>
       </c>
       <c r="K42" t="n">
-        <v>13.69984102249146</v>
+        <v>12.96580910682678</v>
       </c>
       <c r="L42" t="n">
-        <v>14.87751188278198</v>
+        <v>12.66837337017059</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>17.31174802780151</v>
+        <v>15.92293524742126</v>
       </c>
       <c r="C43" t="n">
-        <v>15.76750874519348</v>
+        <v>13.43679428100586</v>
       </c>
       <c r="D43" t="n">
-        <v>18.02978873252869</v>
+        <v>12.97001528739929</v>
       </c>
       <c r="E43" t="n">
-        <v>19.02014517784119</v>
+        <v>13.01911687850952</v>
       </c>
       <c r="F43" t="n">
-        <v>14.26353216171265</v>
+        <v>13.55129981040955</v>
       </c>
       <c r="G43" t="n">
-        <v>18.48511838912964</v>
+        <v>16.99680280685425</v>
       </c>
       <c r="H43" t="n">
-        <v>15.06587743759155</v>
+        <v>12.07657146453857</v>
       </c>
       <c r="I43" t="n">
-        <v>16.12969541549683</v>
+        <v>16.73294067382812</v>
       </c>
       <c r="J43" t="n">
-        <v>11.98007655143738</v>
+        <v>12.45299243927002</v>
       </c>
       <c r="K43" t="n">
-        <v>13.87596940994263</v>
+        <v>12.58295702934265</v>
       </c>
       <c r="L43" t="n">
-        <v>15.99294600486755</v>
+        <v>13.97424259185791</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>14.85214328765869</v>
+        <v>13.89810180664062</v>
       </c>
       <c r="C44" t="n">
-        <v>15.37879228591919</v>
+        <v>16.40632390975952</v>
       </c>
       <c r="D44" t="n">
-        <v>17.6073944568634</v>
+        <v>12.78690767288208</v>
       </c>
       <c r="E44" t="n">
-        <v>17.15949082374573</v>
+        <v>13.14103293418884</v>
       </c>
       <c r="F44" t="n">
-        <v>26.11308836936951</v>
+        <v>17.30244541168213</v>
       </c>
       <c r="G44" t="n">
-        <v>24.55181193351746</v>
+        <v>12.88484573364258</v>
       </c>
       <c r="H44" t="n">
-        <v>13.9370288848877</v>
+        <v>12.2813093662262</v>
       </c>
       <c r="I44" t="n">
-        <v>13.37145042419434</v>
+        <v>13.71539187431335</v>
       </c>
       <c r="J44" t="n">
-        <v>15.2444896697998</v>
+        <v>15.72542476654053</v>
       </c>
       <c r="K44" t="n">
-        <v>15.23811650276184</v>
+        <v>16.85005593299866</v>
       </c>
       <c r="L44" t="n">
-        <v>17.34538066387177</v>
+        <v>14.49918394088745</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>19.15511274337769</v>
+        <v>11.77750754356384</v>
       </c>
       <c r="C45" t="n">
-        <v>18.71821475028992</v>
+        <v>10.6394784450531</v>
       </c>
       <c r="D45" t="n">
-        <v>11.47486853599548</v>
+        <v>12.32708787918091</v>
       </c>
       <c r="E45" t="n">
-        <v>16.97603845596313</v>
+        <v>13.14312982559204</v>
       </c>
       <c r="F45" t="n">
-        <v>11.22637104988098</v>
+        <v>11.15226435661316</v>
       </c>
       <c r="G45" t="n">
-        <v>12.11363077163696</v>
+        <v>11.27825379371643</v>
       </c>
       <c r="H45" t="n">
-        <v>13.11717224121094</v>
+        <v>14.10457587242126</v>
       </c>
       <c r="I45" t="n">
-        <v>14.84422302246094</v>
+        <v>10.95657801628113</v>
       </c>
       <c r="J45" t="n">
-        <v>11.00237441062927</v>
+        <v>11.81142520904541</v>
       </c>
       <c r="K45" t="n">
-        <v>10.95156383514404</v>
+        <v>12.90506625175476</v>
       </c>
       <c r="L45" t="n">
-        <v>13.95795698165893</v>
+        <v>12.0095367193222</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>14.31825947761536</v>
+        <v>17.8125855922699</v>
       </c>
       <c r="C46" t="n">
-        <v>13.44903874397278</v>
+        <v>18.51084351539612</v>
       </c>
       <c r="D46" t="n">
-        <v>12.50143909454346</v>
+        <v>17.6615002155304</v>
       </c>
       <c r="E46" t="n">
-        <v>12.48002457618713</v>
+        <v>19.13970637321472</v>
       </c>
       <c r="F46" t="n">
-        <v>12.54481816291809</v>
+        <v>17.53662371635437</v>
       </c>
       <c r="G46" t="n">
-        <v>18.64344668388367</v>
+        <v>13.20909523963928</v>
       </c>
       <c r="H46" t="n">
-        <v>13.02405762672424</v>
+        <v>15.34134411811829</v>
       </c>
       <c r="I46" t="n">
-        <v>13.34972882270813</v>
+        <v>13.14979887008667</v>
       </c>
       <c r="J46" t="n">
-        <v>14.83337259292603</v>
+        <v>12.53793907165527</v>
       </c>
       <c r="K46" t="n">
-        <v>16.0207576751709</v>
+        <v>12.70301127433777</v>
       </c>
       <c r="L46" t="n">
-        <v>14.11649434566498</v>
+        <v>15.76024479866028</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>13.10826134681702</v>
+        <v>12.61248803138733</v>
       </c>
       <c r="C47" t="n">
-        <v>12.16048622131348</v>
+        <v>12.054283618927</v>
       </c>
       <c r="D47" t="n">
-        <v>18.06047463417053</v>
+        <v>18.74183034896851</v>
       </c>
       <c r="E47" t="n">
-        <v>21.17870473861694</v>
+        <v>11.87805604934692</v>
       </c>
       <c r="F47" t="n">
-        <v>11.9380509853363</v>
+        <v>14.22397232055664</v>
       </c>
       <c r="G47" t="n">
-        <v>16.49590873718262</v>
+        <v>11.41131210327148</v>
       </c>
       <c r="H47" t="n">
-        <v>13.21536207199097</v>
+        <v>14.82543849945068</v>
       </c>
       <c r="I47" t="n">
-        <v>12.19893383979797</v>
+        <v>12.97476506233215</v>
       </c>
       <c r="J47" t="n">
-        <v>12.62878608703613</v>
+        <v>14.36869359016418</v>
       </c>
       <c r="K47" t="n">
-        <v>15.57174777984619</v>
+        <v>12.42966818809509</v>
       </c>
       <c r="L47" t="n">
-        <v>14.65567164421082</v>
+        <v>13.55205078125</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>15.24946451187134</v>
+        <v>12.15688157081604</v>
       </c>
       <c r="C48" t="n">
-        <v>12.50167393684387</v>
+        <v>13.30688619613647</v>
       </c>
       <c r="D48" t="n">
-        <v>13.71904230117798</v>
+        <v>15.39997148513794</v>
       </c>
       <c r="E48" t="n">
-        <v>12.58988428115845</v>
+        <v>13.19620203971863</v>
       </c>
       <c r="F48" t="n">
-        <v>14.24367666244507</v>
+        <v>14.89975333213806</v>
       </c>
       <c r="G48" t="n">
-        <v>12.78345489501953</v>
+        <v>16.08107566833496</v>
       </c>
       <c r="H48" t="n">
-        <v>13.31087231636047</v>
+        <v>12.71363735198975</v>
       </c>
       <c r="I48" t="n">
-        <v>12.61417961120605</v>
+        <v>13.84729886054993</v>
       </c>
       <c r="J48" t="n">
-        <v>13.33380484580994</v>
+        <v>13.43706655502319</v>
       </c>
       <c r="K48" t="n">
-        <v>13.02805423736572</v>
+        <v>13.4669668674469</v>
       </c>
       <c r="L48" t="n">
-        <v>13.33741075992584</v>
+        <v>13.85057399272919</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>12.81513142585754</v>
+        <v>11.7190203666687</v>
       </c>
       <c r="C49" t="n">
-        <v>17.90692496299744</v>
+        <v>11.9224488735199</v>
       </c>
       <c r="D49" t="n">
-        <v>13.18179202079773</v>
+        <v>15.2373788356781</v>
       </c>
       <c r="E49" t="n">
-        <v>12.21641802787781</v>
+        <v>11.90852761268616</v>
       </c>
       <c r="F49" t="n">
-        <v>12.11766695976257</v>
+        <v>11.96687817573547</v>
       </c>
       <c r="G49" t="n">
-        <v>12.40442395210266</v>
+        <v>13.61545991897583</v>
       </c>
       <c r="H49" t="n">
-        <v>11.78801226615906</v>
+        <v>11.94958519935608</v>
       </c>
       <c r="I49" t="n">
-        <v>15.09648442268372</v>
+        <v>12.75004696846008</v>
       </c>
       <c r="J49" t="n">
-        <v>12.62781143188477</v>
+        <v>12.0682737827301</v>
       </c>
       <c r="K49" t="n">
-        <v>12.57794332504272</v>
+        <v>11.3710503578186</v>
       </c>
       <c r="L49" t="n">
-        <v>13.2732608795166</v>
+        <v>12.4508670091629</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>13.1023964881897</v>
+        <v>12.10866594314575</v>
       </c>
       <c r="C50" t="n">
-        <v>12.39094662666321</v>
+        <v>17.27306818962097</v>
       </c>
       <c r="D50" t="n">
-        <v>12.0323634147644</v>
+        <v>13.48415994644165</v>
       </c>
       <c r="E50" t="n">
-        <v>11.8278443813324</v>
+        <v>12.47229385375977</v>
       </c>
       <c r="F50" t="n">
-        <v>12.69314122200012</v>
+        <v>12.86284828186035</v>
       </c>
       <c r="G50" t="n">
-        <v>12.81537413597107</v>
+        <v>12.06827664375305</v>
       </c>
       <c r="H50" t="n">
-        <v>12.27870273590088</v>
+        <v>13.21332144737244</v>
       </c>
       <c r="I50" t="n">
-        <v>13.46816897392273</v>
+        <v>15.06474733352661</v>
       </c>
       <c r="J50" t="n">
-        <v>11.97089242935181</v>
+        <v>12.58225798606873</v>
       </c>
       <c r="K50" t="n">
-        <v>12.70441913604736</v>
+        <v>12.15886545181274</v>
       </c>
       <c r="L50" t="n">
-        <v>12.52842495441437</v>
+        <v>13.32885050773621</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>11.36391663551331</v>
+        <v>11.54147005081177</v>
       </c>
       <c r="C51" t="n">
-        <v>11.21678018569946</v>
+        <v>13.17623257637024</v>
       </c>
       <c r="D51" t="n">
-        <v>11.57982015609741</v>
+        <v>12.14389681816101</v>
       </c>
       <c r="E51" t="n">
-        <v>12.26809358596802</v>
+        <v>11.74992299079895</v>
       </c>
       <c r="F51" t="n">
-        <v>13.23954391479492</v>
+        <v>14.8298134803772</v>
       </c>
       <c r="G51" t="n">
-        <v>11.66714882850647</v>
+        <v>13.09528660774231</v>
       </c>
       <c r="H51" t="n">
-        <v>11.36490345001221</v>
+        <v>11.88670563697815</v>
       </c>
       <c r="I51" t="n">
-        <v>11.35994839668274</v>
+        <v>12.01538443565369</v>
       </c>
       <c r="J51" t="n">
-        <v>11.36742234230042</v>
+        <v>11.56754398345947</v>
       </c>
       <c r="K51" t="n">
-        <v>11.86110591888428</v>
+        <v>12.4008960723877</v>
       </c>
       <c r="L51" t="n">
-        <v>11.72886834144592</v>
+        <v>12.44071526527405</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14.12387167930603</v>
+        <v>13.72231192111969</v>
       </c>
       <c r="C52" t="n">
-        <v>13.41905754089355</v>
+        <v>13.48723452568054</v>
       </c>
       <c r="D52" t="n">
-        <v>13.47891387939453</v>
+        <v>13.39872362613678</v>
       </c>
       <c r="E52" t="n">
-        <v>14.13965106964111</v>
+        <v>12.97940739631653</v>
       </c>
       <c r="F52" t="n">
-        <v>13.3060494184494</v>
+        <v>13.45168642044067</v>
       </c>
       <c r="G52" t="n">
-        <v>14.02606232643127</v>
+        <v>13.12601052284241</v>
       </c>
       <c r="H52" t="n">
-        <v>13.86257897853851</v>
+        <v>13.56222681999207</v>
       </c>
       <c r="I52" t="n">
-        <v>14.09643255710602</v>
+        <v>13.35703866004944</v>
       </c>
       <c r="J52" t="n">
-        <v>13.99788759708404</v>
+        <v>13.10254318237305</v>
       </c>
       <c r="K52" t="n">
-        <v>13.61492533683777</v>
+        <v>13.6852774477005</v>
       </c>
       <c r="L52" t="n">
-        <v>13.80654303836823</v>
+        <v>13.38724605226517</v>
       </c>
     </row>
   </sheetData>
